--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,42 +481,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IE0003YRHWF4</t>
+          <t>IE00BD2PJG29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sustainable Future Connectivity FAM Fund</t>
+          <t>FAM MSCI Emerging Markets Index Fund</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>technology cloud connectivity artificial intelligence semiconductors</t>
+          <t>emerging markets China India equities dollar rates</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Azioni, da Microsoft ad Alibaba: i titoli dell’Ai da mettere nel radar - We Wealth</t>
+          <t>The new hierarchies of the currency market - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>We Wealth</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Wed, 17 Sep 2025 07:00:00 GMT</t>
+          <t>Thu, 21 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNWpXOVA4ZTE5SDVGYnBPWW8zdVVITmlXYzFucGozSEtBaTBWdHNBUktzZ2NJYWVVRUFnejB2SEV6am9qUXl2aWQxLURwOHVLWlk3TlYteFNPSDJwRjNWbENPSGVFU3lKaks3UF9KYzNBaWNxVVBKTlJEMkZocWtBN0xGbFo3QlBmOEs0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5ENUZmYV9HQzdUV0Z2S2RjQ3FsUm9xWkkxT19xRXVuS1dILU1NUGRJQTU5cXJ6S296ajVIRUlseThsMG41SFI0ZkNNdUh6ZG1pem50RUh2cHVxaFNQcXMycmY1b2dwNDZwSEZNSHkwbjdYVm1QZjVTWk1xUlpRdw?oc=5</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -534,34 +534,34 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IE0003YRHWF4</t>
+          <t>IE00BD2PJG29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sustainable Future Connectivity FAM Fund</t>
+          <t>FAM MSCI Emerging Markets Index Fund</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>technology cloud connectivity artificial intelligence semiconductors</t>
+          <t>emerging markets China India equities dollar rates</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6G is quietly making headway – the telecommunications network that sees - Il Sole 24 ORE</t>
+          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 07:29:45 GMT</t>
+          <t>Sat, 05 Oct 2024 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOcmxhcHk4ZlhWME5GRFdKRXY3eWZQN3VIQWRQYUo2Y2VXZ1c2WW5vdmJKRXlsODhxZHR2Ym16Qlh6M3hOM2tVa1lNdFBHUTc0NTJGMlFSRDZUc29BRTJCb1NlQ04wNEdaYXBmd2c4b3NoM2ZQdWZ3WjRxUHJmQUZmenMzb1ZIejZLSEVKdC0wRnJfSzFZRTI5VWdrN2xHWXJkY21B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPNVNWZkg1OXdPY01La05BQnBCa0JVU29KY0xocVM3aktBTEJTaFgzbHljME8tcVJCb09lV2VQd0pZblE1ZnA4Q2F5ZVVjZFVxbGk1U0xiMktUNVlvVWdTX1Ywa2FMRUx6UnpLS2lfbmFGNjNyVEtIc2tIRVAwVFRaRXFwYmxOLTBrdGJr?oc=5</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -594,109 +594,109 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IE0003YRHWF4</t>
+          <t>IE00BD2PJG29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sustainable Future Connectivity FAM Fund</t>
+          <t>FAM MSCI Emerging Markets Index Fund</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>technology cloud connectivity artificial intelligence semiconductors</t>
+          <t>emerging markets China India equities dollar rates</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NOK Stock Rises Pre-Market: Trump Endorsement Adds Fuel To AI Growth Push For Nokia - TradingView</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOcXhwQURoelZZNkZkLVZKVkM3ZWdMZnV0RE5WWEhqYzdESndCZUthYW53a3MtY1dvTnpIazEzdXRlQ29aU0hzS25YbjFyLVQtaDFiTnVvZ0steUoxRFhBRl9MWm9nUHBfbVhmS0dLU3hxUVhDT0dOUTR2Sm00UGxzaXB1MjhEclZXTWRyUGUwSU9LbzZsemt3OWx6WDhPdHk2dl9DRXVyT3QyOFA2VVBoWXFHVV9WbTZRcFU4SUxlWWlmYlM3Slg2Wm9ZWmlqTjhpajRSZnF6cVhVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Potrebbe supportare fondi tech/AI nel breve</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IE0003YRHWF4</t>
+          <t>IE00BD2PJG29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sustainable Future Connectivity FAM Fund</t>
+          <t>FAM MSCI Emerging Markets Index Fund</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>technology cloud connectivity artificial intelligence semiconductors</t>
+          <t>emerging markets China India equities dollar rates</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Google may work with Samsung to make key component of next-gen Tensor chip: All details - The Times of India</t>
+          <t>Pernod Ricard's stock market plunges after a difficult 2026: US and China slow revenues, focusing on India - Montenapo Daily</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Montenapo Daily</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 07:38:14 GMT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNUm1tcEt4SnlRYmlzOW40d2VjOGZSUE9JR2w2bnllTG1mR1FfclpwMXJaTFpDc0hkMUctTWNNZFFzaEgyeUJ6Z3c4aHhpUGxHdXhVWVZMemhhYlcwQXNFTHRVZDQ0OHFZbFF1VmhHbnJFTVExZFFrdEZ4bG9hTzRnZVcxS0lOV1NtMll6Q21EU2JfXzB3VHp6OVRRakF4dG9Fa2NqM0JSQjVtamh2SkNSbW5haHpXaklMN3lydnZlSVlpOXppUFdHMzdnTldXNFdmNGMzQVZGdHQtQU4tMXh1WGJJZW5KMVdjX2V4ZVZn0gHzAUFVX3lxTE9sSlZvQldLVWJmNzdmSjhyazdIU3lNMV9wWkdVRWtjWjdSVlhCOFhUWXlLNkZLZVQ4a2lFQzRfTjdXR21tNlZhYmRjOHZTbWsyZVZXZklWcjhqdG5rWE1DdUxwNEE2U1VTMTBZOTVpSlJralQ4Q3FTVkF4aVM0b2NzQlZXcHZBand5TzFHei1COUhua1J1Y1hhdXUtQVFISVBHT0dDb3BmNWYtTE1WMXR6TWF2VlI0cWlFTllHX2hHc2swUUtLOUhWYndsNXJkT3NxejFJWndHSzZaWGhISGNhS1ZvNFd5N0g0SlZOSzRhWkZMbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTDNqMmcySUVOZTFhNnJ4ZVJBal9xVkJDXzRBTFZ1czhOVmhWcVFId0sxbVcxWmx2WUZvRXRmcUJVZGxsY1c1a3BiWjd5SWtiaWJuSnloN0VaaU04OVFLbUdfN1IzcHliQXlfWm9qenl6SVBIaTc3VEpockNxRWR3WWt4QU9fNVJhVTA5RHRBOTdVVmZHSmhOVjFoNWZzXzZTR3lQMjQwUHVCYkgyZTJUdUZ2VlJXUnd2NXpWSkZJeF9NZVZDSVpRazQtUkI1WmktdjlSQmZQamgxUQ?oc=5</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -714,34 +714,34 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IE0003YRHWF4</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sustainable Future Connectivity FAM Fund</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>technology cloud connectivity artificial intelligence semiconductors</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Extreme Networks Announces Investor Conferences for August and September 2026 - 01net</t>
+          <t>Capital One Announces Quarterly Dividend - 01net</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 23:05:00 GMT</t>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNMXZXd3lvRlRSTmxXR1hXZ1NBZEQxY3ZWY3g2UnpMQUhvX0s4YmE3ZlJ6NGpJWGJPdXV3N05RSF8weTR1UVNBZUxWQ012bU93LUtmWXNFM0YwQndnQlZpdUFHbUkxclZxaERjbmM1eWt6TWhrZHp5NXFxdENNSDZ6aHpPXzN0MmRZTXhIaGtGUi1hcmRKT1M4QXg3aUFmSGN2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -774,49 +774,49 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IE00BD2PJG29</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FAM MSCI Emerging Markets Index Fund</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>emerging markets China India equities dollar rates</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The new hierarchies of the currency market - Il Sole 24 ORE</t>
+          <t>Gli ETF più popolari del trimestre - Morningstar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thu, 21 May 2026 07:00:00 GMT</t>
+          <t>Sat, 28 Jun 2025 23:59:51 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5ENUZmYV9HQzdUV0Z2S2RjQ3FsUm9xWkkxT19xRXVuS1dILU1NUGRJQTU5cXJ6S296ajVIRUlseThsMG41SFI0ZkNNdUh6ZG1pem50RUh2cHVxaFNQcXMycmY1b2dwNDZwSEZNSHkwbjdYVm1QZjVTWk1xUlpRdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbDFGNWY3WS1FT0tmdkZMc1k4QlVLUmhQOExzcE45T1VmWDBYWGZOeENJVGFhMS16ajcydFNaUFdwRkNxZ183X1AxNkh0NGR0RGdyYzN0Q196bndPVDRNWVBKQi1JZ1oyaDJHWTA2Qlc1ZmxaamI1Tm1sN2tRWnloTmN3?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,49 +834,49 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IE00BD2PJG29</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FAM MSCI Emerging Markets Index Fund</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>emerging markets China India equities dollar rates</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
+          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sat, 05 Oct 2024 07:00:00 GMT</t>
+          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPNVNWZkg1OXdPY01La05BQnBCa0JVU29KY0xocVM3aktBTEJTaFgzbHljME8tcVJCb09lV2VQd0pZblE1ZnA4Q2F5ZVVjZFVxbGk1U0xiMktUNVlvVWdTX1Ywa2FMRUx6UnpLS2lfbmFGNjNyVEtIc2tIRVAwVFRaRXFwYmxOLTBrdGJr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,49 +894,49 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IE00BD2PJG29</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FAM MSCI Emerging Markets Index Fund</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>emerging markets China India equities dollar rates</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -954,49 +954,49 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IE00BD2PJG29</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FAM MSCI Emerging Markets Index Fund</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>emerging markets China India equities dollar rates</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pernod Ricard's stock market plunges after a difficult 2026: US and China slow revenues, focusing on India - Montenapo Daily</t>
+          <t>IG Stock Price and Chart — MIL:IG - TradingView</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montenapo Daily</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 07:38:14 GMT</t>
+          <t>Sat, 22 Jul 2017 22:31:42 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTDNqMmcySUVOZTFhNnJ4ZVJBal9xVkJDXzRBTFZ1czhOVmhWcVFId0sxbVcxWmx2WUZvRXRmcUJVZGxsY1c1a3BiWjd5SWtiaWJuSnloN0VaaU04OVFLbUdfN1IzcHliQXlfWm9qenl6SVBIaTc3VEpockNxRWR3WWt4QU9fNVJhVTA5RHRBOTdVVmZHSmhOVjFoNWZzXzZTR3lQMjQwUHVCYkgyZTJUdUZ2VlJXUnd2NXpWSkZJeF9NZVZDSVpRazQtUkI1WmktdjlSQmZQamgxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1FdGROWlJaTTNyWDU5R29SSE5fQzFXMXJmMEhHUTEzTVhnVjV4YkRCV1FGZEdMU2gtVTBOM05qZ0JaNVpmMGU5YnhsZkdad3NzZjY1LUFB?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1014,109 +1014,109 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 06:15:19 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gli ETF più popolari del trimestre - Morningstar</t>
+          <t>A record-breaking week for European stock markets, but doubts remain over bonds - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sat, 28 Jun 2025 23:59:51 GMT</t>
+          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbDFGNWY3WS1FT0tmdkZMc1k4QlVLUmhQOExzcE45T1VmWDBYWGZOeENJVGFhMS16ajcydFNaUFdwRkNxZ183X1AxNkh0NGR0RGdyYzN0Q196bndPVDRNWVBKQi1JZ1oyaDJHWTA2Qlc1ZmxaamI1Tm1sN2tRWnloTmN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1134,49 +1134,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
+          <t>From refuge to coexistence: why gold and equities no longer take turns - ilsole24ore.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>ilsole24ore.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
+          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1194,49 +1194,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1254,49 +1254,49 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IG Stock Price and Chart — MIL:IG - TradingView</t>
+          <t>IMF: global growth resilient (for now) to tensions and tariffs. Artificial intelligence uncertain - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sat, 22 Jul 2017 22:31:42 GMT</t>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1FdGROWlJaTTNyWDU5R29SSE5fQzFXMXJmMEhHUTEzTVhnVjV4YkRCV1FGZEdMU2gtVTBOM05qZ0JaNVpmMGU5YnhsZkdad3NzZjY1LUFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWmVJdjR6ZWdNR3IwNnFwRUNnQllhRFhCYXR2WXMzWDhBdXUtMVc4djM1X2h4QldNRUFMeXB2VUp5WFN1ZlFVUTU3SHpqdG12Yl9sRm9XSzlJSkM2bkdfUndiamRUSjMzMFZINDIySk5OSUJrbzNfUUN6SlY1ZWVwb29tc2QteDdNUVdpd3VGa3RQNEpTV19mXy01ODBsd3dkNlExVEpKZUd6SDhfUWRGRTl3MkdXNThHWlZvWmVOOA?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1314,24 +1314,24 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1374,24 +1374,24 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1401,22 +1401,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CIO Weekly: What Happens If No One Hikes? - Neuberger Berman</t>
+          <t>A record-breaking week for European stock markets, but doubts remain over bonds - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 01:41:45 GMT</t>
+          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNMHNmWVc0YmhqQnBtcHBJaTZwN3dIdFB2Yld5ZGdHRExVaGs2VWRtQnY2a2NxaGxGR3V2dGZOc29ySWVJSTJhUDdyRy1YdGh3NnFiV3l2a0RPSmJOMllITXdOQTVaQ3pTTFRRR3A5VU5uSTcwX2xid25FOGx3dG5OcVR1M0o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1434,24 +1434,24 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1461,22 +1461,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A record-breaking week for European stock markets, but doubts remain over bonds - Il Sole 24 ORE</t>
+          <t>From refuge to coexistence: why gold and equities no longer take turns - ilsole24ore.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>ilsole24ore.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1494,24 +1494,24 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1521,22 +1521,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>From refuge to coexistence: why gold and equities no longer take turns - Il Sole 24 ORE</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
+          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1554,24 +1554,24 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1581,22 +1581,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>IMF: global growth resilient (for now) to tensions and tariffs. Artificial intelligence uncertain - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWmVJdjR6ZWdNR3IwNnFwRUNnQllhRFhCYXR2WXMzWDhBdXUtMVc4djM1X2h4QldNRUFMeXB2VUp5WFN1ZlFVUTU3SHpqdG12Yl9sRm9XSzlJSkM2bkdfUndiamRUSjMzMFZINDIySk5OSUJrbzNfUUN6SlY1ZWVwb29tc2QteDdNUVdpd3VGa3RQNEpTV19mXy01ODBsd3dkNlExVEpKZUd6SDhfUWRGRTl3MkdXNThHWlZvWmVOOA?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1614,34 +1614,34 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,117 +1651,117 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 06:15:19 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CIO Weekly: What Happens If No One Hikes? - Neuberger Berman</t>
+          <t>Stock market: shares open higher following Wall Street’s rally, with Milan immediately above the 52,000 mark - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 01:41:45 GMT</t>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNMHNmWVc0YmhqQnBtcHBJaTZwN3dIdFB2Yld5ZGdHRExVaGs2VWRtQnY2a2NxaGxGR3V2dGZOc29ySWVJSTJhUDdyRy1YdGh3NnFiV3l2a0RPSmJOMllITXdOQTVaQ3pTTFRRR3A5VU5uSTcwX2xid25FOGx3dG5OcVR1M0o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOUlRaVpqSHBQaUFiUVpWSHAzd09ZUkQ5QXZjYVRuMTVQUGtkcEpHS1hHbkNRVlotNHRwQ1BrQUE2ZENBOVRHcTZqb3B2T3pwcnVQdXdrekthNVo5UThBei1fV3dWZjlEbncyajUwRlMzV0pEZlhVVm5ia0JEczRPZkFINUpQbWE0US1ES01Qc29LZTNfUGs3U1JDcjZOaDJJQ2pDSmZGOGpBWWVtRldTamtVUVFiZThsTHhrX0loVGhOcmhTeDlsVQ?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>A record-breaking week for European stock markets, but doubts remain over bonds - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1794,109 +1794,109 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>From refuge to coexistence: why gold and equities no longer take turns - Il Sole 24 ORE</t>
+          <t>Stock Market Today January 27: Nasdaq Deep in the Red, Nvidia Collapses. Milan Looks to Risk, Mps Still Down - LIVE - firstonline.info</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>firstonline.info</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
+          <t>Mon, 27 Jan 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxORS15UkozMVZ6anBOcUNGNmx0NHNWODdsLUpDYVVUS2FsbXdrcW1meVd0RWxsck5zd0VNODl3Wko2VXZLZG0tWUxySldWRC12T0I3UlMzdld5dVM2eW5uT1NTX3kyVkVnTE8weVBCLWZ2bWswSThLeUpLRXdSWnlQUThKNHNTX0ZuVUN6OUFfd3laOHRfSXJ2OE01bldvdlRTY1FfN3BROWpvSmxUcVFFaDFDWU9oa2hjTnltS2tjaWg3eDZLLWNRSFh5OC10eXg0ZHR6N3laOUkxeGlSOHRrNnd4VQ?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1914,49 +1914,49 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Equity Market Commentary - June 2026 - Morgan Stanley</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mon, 31 Aug 2026 04:21:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQQlNQaE12RW5CN0hfbXRDRlZiSG9rUllBak5VdXh2d3BQNTJXS2x6bWZzMEJyenFFdzIyMjNrZEpEbnlzUFRqSFZCZThfcGxkVFlDbWR6R3lsQzkwM19DeTZNZkVMUXFiWnZubEs1dkNhRk02RXZkVVR2cS12VGMwdE5iYTBQZy1ZUU1OQldhMjc3SE9CTFU0Ty16X0x3ODZNeVFRMUNqQ05wU3d0cHprSE1MLTF1aVdOLVZ0WVpYU3FhUDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1974,109 +1974,109 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>No. 66 - Is there an equity greenium in the euro area? - bancaditalia.it</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>bancaditalia.it</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tue, 07 Oct 2025 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPbjQzOGJBUDZqRUlkQXJoZlVVTWdSRFZXTnlrZmlPNjQ3cWNCSktOZ2tzUFRjcUpBZ0MtLVZxSEh1eXU4M3ZEOW0yWjAyRHdYWTEwV2V0dVBuSEQwdGJYdVpST0dWbVpyU2hzc095QUcxX1djWWhmNjVKVzJ2dmY4REdJejdYS0Nrb0pBLUZDLTNvRm9rNmhKeVhzakN1R1N2cHNTc3lrNlh1VUJRTlZtOTJ6QWotVWYzODlwcW1VN2ljbTgzLTNyRlZfa2UyR1hhYWRfazlMaFpSN1hsRGI2YVFuRG5VQUVmY0tweG9idjlQZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2094,34 +2094,34 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>'Unipol stands out for its dividend' - Il Sole 24 ORE</t>
+          <t>ECB and Eurozone central banks: we need a single market with the same deposit guarantees - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 07:00:00 GMT</t>
+          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE82TDltZHpPajV4LUg3Zk5EU2c4SlhZa3dSWk5wZ1ZCNGlhVnlFbFg4SHRjMXhucE85eEt6Uy1mNlpFdkRuekpKeHVPcTdBZ0NybGhxMTNkZmxKRE1HNVp2ZnBsc1dWaGNzM3d6R3ptMXlUaXVO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPc3dNeE5QRkFBM0Vmck44N2tJcGJialpMY3VFUF9FLTJDYVl4WUxFem9zTEZXejlZWVN1aHR2aDdLRFJwc2NpbTdtSzUyODF6X3B4ZERLLTVVZ0VfbFhNMWRqczRJbjVZWXlGamxwbWhNY0FHVUVwRHVjZ2FRaFJsZ3l2Y1Z6SnBLd245blhNVmxZU0VoMFFFSWZpaVFiQjVQb1pUM2U3YVBDRVU5ZXdzRnlxRQ?oc=5</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Stock markets: Europe takes a breather after a record half-year; Milan down 0.15 per cent. Wall Street in the red - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2191,330 +2191,30 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmw4QWxUeXBEWHprbkxrd0RNX3ZUTkJmXzc4TkF5LTEtYVl4T1JOQkdBV2QwTndjWHJFOWt2MGNpdEFCQklpTldPTHlzWlY2M1JOOGJubWc2cUlRdlRtT2Y0UnA1WHUtalo4U2ZNSkdtbk4xajY0R1NRX19CV1VRWFhDNUlJRUhfemc?oc=5</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe pesare su azionario europeo</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-09-02T13:37:04+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:04+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>La Stampa</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:04+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:04+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ECB and Eurozone central banks: we need a single market with the same deposit guarantees - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPc3dNeE5QRkFBM0Vmck44N2tJcGJialpMY3VFUF9FLTJDYVl4WUxFem9zTEZXejlZWVN1aHR2aDdLRFJwc2NpbTdtSzUyODF6X3B4ZERLLTVVZ0VfbFhNMWRqczRJbjVZWXlGamxwbWhNY0FHVUVwRHVjZ2FRaFJsZ3l2Y1Z6SnBLd245blhNVmxZU0VoMFFFSWZpaVFiQjVQb1pUM2U3YVBDRVU5ZXdzRnlxRQ?oc=5</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:04+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Stock markets: Europe takes a breather after a record half-year; Milan down 0.15 per cent. Wall Street in the red - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmw4QWxUeXBEWHprbkxrd0RNX3ZUTkJmXzc4TkF5LTEtYVl4T1JOQkdBV2QwTndjWHJFOWt2MGNpdEFCQklpTldPTHlzWlY2M1JOOGJubWc2cUlRdlRtT2Y0UnA1WHUtalo4U2ZNSkdtbk4xajY0R1NRX19CV1VRWFhDNUlJRUhfemc?oc=5</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Attenzione / pressione negativa</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Potrebbe pesare su azionario europeo</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:04+00:00</t>
+          <t>2026-09-02T14:16:17+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -654,49 +654,49 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IE00BD2PJG29</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FAM MSCI Emerging Markets Index Fund</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>emerging markets China India equities dollar rates</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pernod Ricard's stock market plunges after a difficult 2026: US and China slow revenues, focusing on India - Montenapo Daily</t>
+          <t>Capital One Announces Quarterly Dividend - 01net</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Montenapo Daily</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 07:38:14 GMT</t>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTDNqMmcySUVOZTFhNnJ4ZVJBal9xVkJDXzRBTFZ1czhOVmhWcVFId0sxbVcxWmx2WUZvRXRmcUJVZGxsY1c1a3BiWjd5SWtiaWJuSnloN0VaaU04OVFLbUdfN1IzcHliQXlfWm9qenl6SVBIaTc3VEpockNxRWR3WWt4QU9fNVJhVTA5RHRBOTdVVmZHSmhOVjFoNWZzXzZTR3lQMjQwUHVCYkgyZTJUdUZ2VlJXUnd2NXpWSkZJeF9NZVZDSVpRazQtUkI1WmktdjlSQmZQamgxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -741,22 +741,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net</t>
+          <t>3 titoli ad alto dividendo per il mese di settembre - Morningstar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+          <t>Fri, 05 Sep 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNUTRONmdsT0RIc2NWbkxSdmlOLVl3cmxZYXV5SnNweF9lMUszQ3VxVFRoa3UyV2F2WWM1SlVzVFV6OHZkazlBZmlPUVBVcF9EdksyZC1SOHg5OTJnNHpYNlRQSkxtdlZXRks1ckhzYmw0cFpVaF8tUGZaUE51WkhobnVmRmxMdUtEZENqVXdTTmxGZVBxeU9V?oc=5</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -801,22 +801,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gli ETF più popolari del trimestre - Morningstar</t>
+          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sat, 28 Jun 2025 23:59:51 GMT</t>
+          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbDFGNWY3WS1FT0tmdkZMc1k4QlVLUmhQOExzcE45T1VmWDBYWGZOeENJVGFhMS16ajcydFNaUFdwRkNxZ183X1AxNkh0NGR0RGdyYzN0Q196bndPVDRNWVBKQi1JZ1oyaDJHWTA2Qlc1ZmxaamI1Tm1sN2tRWnloTmN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
+          <t>Gli ETF più popolari del trimestre - Morningstar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
+          <t>Sat, 28 Jun 2025 23:59:51 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbDFGNWY3WS1FT0tmdkZMc1k4QlVLUmhQOExzcE45T1VmWDBYWGZOeENJVGFhMS16ajcydFNaUFdwRkNxZ183X1AxNkh0NGR0RGdyYzN0Q196bndPVDRNWVBKQi1JZ1oyaDJHWTA2Qlc1ZmxaamI1Tm1sN2tRWnloTmN3?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -954,67 +954,67 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IG Stock Price and Chart — MIL:IG - TradingView</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sat, 22 Jul 2017 22:31:42 GMT</t>
+          <t>Tue, 01 Sep 2026 06:15:19 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1FdGROWlJaTTNyWDU5R29SSE5fQzFXMXJmMEhHUTEzTVhnVjV4YkRCV1FGZEdMU2gtVTBOM05qZ0JaNVpmMGU5YnhsZkdad3NzZjY1LUFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,40 +1041,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>CIO Weekly: What Happens If No One Hikes? - Neuberger Berman</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 06:15:19 GMT</t>
+          <t>Mon, 24 Aug 2026 01:41:45 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNMHNmWVc0YmhqQnBtcHBJaTZwN3dIdFB2Yld5ZGdHRExVaGs2VWRtQnY2a2NxaGxGR3V2dGZOc29ySWVJSTJhUDdyRy1YdGh3NnFiV3l2a0RPSmJOMllITXdOQTVaQ3pTTFRRR3A5VU5uSTcwX2xid25FOGx3dG5OcVR1M0o?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A record-breaking week for European stock markets, but doubts remain over bonds - Il Sole 24 ORE</t>
+          <t>From refuge to coexistence: why gold and equities no longer take turns - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,22 +1161,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>From refuge to coexistence: why gold and equities no longer take turns - ilsole24ore.com</t>
+          <t>IMF: global growth resilient (for now) to tensions and tariffs. Artificial intelligence uncertain - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWmVJdjR6ZWdNR3IwNnFwRUNnQllhRFhCYXR2WXMzWDhBdXUtMVc4djM1X2h4QldNRUFMeXB2VUp5WFN1ZlFVUTU3SHpqdG12Yl9sRm9XSzlJSkM2bkdfUndiamRUSjMzMFZINDIySk5OSUJrbzNfUUN6SlY1ZWVwb29tc2QteDdNUVdpd3VGa3RQNEpTV19mXy01ODBsd3dkNlExVEpKZUd6SDhfUWRGRTl3MkdXNThHWlZvWmVOOA?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1254,24 +1254,24 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMF: global growth resilient (for now) to tensions and tariffs. Artificial intelligence uncertain - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1291,30 +1291,30 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 06:15:19 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWmVJdjR6ZWdNR3IwNnFwRUNnQllhRFhCYXR2WXMzWDhBdXUtMVc4djM1X2h4QldNRUFMeXB2VUp5WFN1ZlFVUTU3SHpqdG12Yl9sRm9XSzlJSkM2bkdfUndiamRUSjMzMFZINDIySk5OSUJrbzNfUUN6SlY1ZWVwb29tc2QteDdNUVdpd3VGa3RQNEpTV19mXy01ODBsd3dkNlExVEpKZUd6SDhfUWRGRTl3MkdXNThHWlZvWmVOOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,40 +1341,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>CIO Weekly: What Happens If No One Hikes? - Neuberger Berman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 06:15:19 GMT</t>
+          <t>Mon, 24 Aug 2026 01:41:45 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNMHNmWVc0YmhqQnBtcHBJaTZwN3dIdFB2Yld5ZGdHRExVaGs2VWRtQnY2a2NxaGxGR3V2dGZOc29ySWVJSTJhUDdyRy1YdGh3NnFiV3l2a0RPSmJOMllITXdOQTVaQ3pTTFRRR3A5VU5uSTcwX2xid25FOGx3dG5OcVR1M0o?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A record-breaking week for European stock markets, but doubts remain over bonds - Il Sole 24 ORE</t>
+          <t>From refuge to coexistence: why gold and equities no longer take turns - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,22 +1461,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>From refuge to coexistence: why gold and equities no longer take turns - ilsole24ore.com</t>
+          <t>IMF: global growth resilient (for now) to tensions and tariffs. Artificial intelligence uncertain - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWmVJdjR6ZWdNR3IwNnFwRUNnQllhRFhCYXR2WXMzWDhBdXUtMVc4djM1X2h4QldNRUFMeXB2VUp5WFN1ZlFVUTU3SHpqdG12Yl9sRm9XSzlJSkM2bkdfUndiamRUSjMzMFZINDIySk5OSUJrbzNfUUN6SlY1ZWVwb29tc2QteDdNUVdpd3VGa3RQNEpTV19mXy01ODBsd3dkNlExVEpKZUd6SDhfUWRGRTl3MkdXNThHWlZvWmVOOA?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,34 +1554,34 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IMF: global growth resilient (for now) to tensions and tariffs. Artificial intelligence uncertain - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1591,30 +1591,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWmVJdjR6ZWdNR3IwNnFwRUNnQllhRFhCYXR2WXMzWDhBdXUtMVc4djM1X2h4QldNRUFMeXB2VUp5WFN1ZlFVUTU3SHpqdG12Yl9sRm9XSzlJSkM2bkdfUndiamRUSjMzMFZINDIySk5OSUJrbzNfUUN6SlY1ZWVwb29tc2QteDdNUVdpd3VGa3RQNEpTV19mXy01ODBsd3dkNlExVEpKZUd6SDhfUWRGRTl3MkdXNThHWlZvWmVOOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>Stock market: shares open higher following Wall Street’s rally, with Milan immediately above the 52,000 mark - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,30 +1651,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOUlRaVpqSHBQaUFiUVpWSHAzd09ZUkQ5QXZjYVRuMTVQUGtkcEpHS1hHbkNRVlotNHRwQ1BrQUE2ZENBOVRHcTZqb3B2T3pwcnVQdXdrekthNVo5UThBei1fV3dWZjlEbncyajUwRlMzV0pEZlhVVm5ia0JEczRPZkFINUpQbWE0US1ES01Qc29LZTNfUGs3U1JDcjZOaDJJQ2pDSmZGOGpBWWVtRldTamtVUVFiZThsTHhrX0loVGhOcmhTeDlsVQ?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stock market: shares open higher following Wall Street’s rally, with Milan immediately above the 52,000 mark - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,30 +1711,30 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOUlRaVpqSHBQaUFiUVpWSHAzd09ZUkQ5QXZjYVRuMTVQUGtkcEpHS1hHbkNRVlotNHRwQ1BrQUE2ZENBOVRHcTZqb3B2T3pwcnVQdXdrekthNVo5UThBei1fV3dWZjlEbncyajUwRlMzV0pEZlhVVm5ia0JEczRPZkFINUpQbWE0US1ES01Qc29LZTNfUGs3U1JDcjZOaDJJQ2pDSmZGOGpBWWVtRldTamtVUVFiZThsTHhrX0loVGhOcmhTeDlsVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,40 +1761,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Stock Market Today January 27: Nasdaq Deep in the Red, Nvidia Collapses. Milan Looks to Risk, Mps Still Down - LIVE - firstonline.info</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>firstonline.info</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 27 Jan 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxORS15UkozMVZ6anBOcUNGNmx0NHNWODdsLUpDYVVUS2FsbXdrcW1meVd0RWxsck5zd0VNODl3Wko2VXZLZG0tWUxySldWRC12T0I3UlMzdld5dVM2eW5uT1NTX3kyVkVnTE8weVBCLWZ2bWswSThLeUpLRXdSWnlQUThKNHNTX0ZuVUN6OUFfd3laOHRfSXJ2OE01bldvdlRTY1FfN3BROWpvSmxUcVFFaDFDWU9oa2hjTnltS2tjaWg3eDZLLWNRSFh5OC10eXg0ZHR6N3laOUkxeGlSOHRrNnd4VQ?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,67 +1821,67 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stock Market Today January 27: Nasdaq Deep in the Red, Nvidia Collapses. Milan Looks to Risk, Mps Still Down - LIVE - firstonline.info</t>
+          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>firstonline.info</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mon, 27 Jan 2025 08:00:00 GMT</t>
+          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxORS15UkozMVZ6anBOcUNGNmx0NHNWODdsLUpDYVVUS2FsbXdrcW1meVd0RWxsck5zd0VNODl3Wko2VXZLZG0tWUxySldWRC12T0I3UlMzdld5dVM2eW5uT1NTX3kyVkVnTE8weVBCLWZ2bWswSThLeUpLRXdSWnlQUThKNHNTX0ZuVUN6OUFfd3laOHRfSXJ2OE01bldvdlRTY1FfN3BROWpvSmxUcVFFaDFDWU9oa2hjTnltS2tjaWg3eDZLLWNRSFh5OC10eXg0ZHR6N3laOUkxeGlSOHRrNnd4VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,22 +2001,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>ECB and Eurozone central banks: we need a single market with the same deposit guarantees - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPc3dNeE5QRkFBM0Vmck44N2tJcGJialpMY3VFUF9FLTJDYVl4WUxFem9zTEZXejlZWVN1aHR2aDdLRFJwc2NpbTdtSzUyODF6X3B4ZERLLTVVZ0VfbFhNMWRqczRJbjVZWXlGamxwbWhNY0FHVUVwRHVjZ2FRaFJsZ3l2Y1Z6SnBLd245blhNVmxZU0VoMFFFSWZpaVFiQjVQb1pUM2U3YVBDRVU5ZXdzRnlxRQ?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>Stock market: Europe weighed down by banks and tech; MPS surge fails to lift Milan (-0.8%) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 19 Aug 2026 16:06:01 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxObzAybVNtTDczVENhSUFxb29RbExsTlp5TVc3dmhxdUR1MUhtb3ZvVk44VUpfTlQ3bGlPaV9LLTFEZ3dFd0xLLWtJeGZsWlhUMEcwVFc2V3ViX2k5RENaTlNwNEVPYkFCUnc1OTRET1NtaFNWc1FpQTFmcFBlSllReTZINVdzXzVtMFhrWk04UElVZEc2SC1wMlhMM3hieFVSU3VyUGpadkJDNzgyOWRYbnh6dllyQklXRGY5RExOQ003MHQ5YUhBWndzc0pHd1NCR2c?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ECB and Eurozone central banks: we need a single market with the same deposit guarantees - Il Sole 24 ORE</t>
+          <t>EU stock exchanges and Wall Street in the red on inflation fears, Milan -2% - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2131,90 +2131,30 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
+          <t>Thu, 14 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPc3dNeE5QRkFBM0Vmck44N2tJcGJialpMY3VFUF9FLTJDYVl4WUxFem9zTEZXejlZWVN1aHR2aDdLRFJwc2NpbTdtSzUyODF6X3B4ZERLLTVVZ0VfbFhNMWRqczRJbjVZWXlGamxwbWhNY0FHVUVwRHVjZ2FRaFJsZ3l2Y1Z6SnBLd245blhNVmxZU0VoMFFFSWZpaVFiQjVQb1pUM2U3YVBDRVU5ZXdzRnlxRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQMjhXUGRDb1BzeGlrNG9vX3JwaVVoVGR4WGFnQUM5N2pnVERfbTZUTGRmemVpdkZFcWFJNlVfVHk5OVAzaUIxbjdObUZxaDJWdjkwM3UzdUltVDZjZDlqZ0lleTdfekhDTHl3WkFlZVZXSGtMLTVhRi12MDNqOVZseGdrNlVvUG13?oc=5</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe pesare su azionario europeo</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:17+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Stock markets: Europe takes a breather after a record half-year; Milan down 0.15 per cent. Wall Street in the red - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmw4QWxUeXBEWHprbkxrd0RNX3ZUTkJmXzc4TkF5LTEtYVl4T1JOQkdBV2QwTndjWHJFOWt2MGNpdEFCQklpTldPTHlzWlY2M1JOOGJubWc2cUlRdlRtT2Y0UnA1WHUtalo4U2ZNSkdtbk4xajY0R1NRX19CV1VRWFhDNUlJRUhfemc?oc=5</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Attenzione / pressione negativa</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Potrebbe pesare su azionario europeo</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-09-02T14:16:17+00:00</t>
+          <t>2026-09-02T21:11:28+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sat, 05 Oct 2024 07:00:00 GMT</t>
+          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPNVNWZkg1OXdPY01La05BQnBCa0JVU29KY0xocVM3aktBTEJTaFgzbHljME8tcVJCb09lV2VQd0pZblE1ZnA4Q2F5ZVVjZFVxbGk1U0xiMktUNVlvVWdTX1Ywa2FMRUx6UnpLS2lfbmFGNjNyVEtIc2tIRVAwVFRaRXFwYmxOLTBrdGJr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -594,49 +594,49 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IE00BD2PJG29</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FAM MSCI Emerging Markets Index Fund</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>emerging markets China India equities dollar rates</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Dividend Aristocrats: migliori azioni a dividendo crescente 2026 - Investing.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB0TktUb19nYXlxR0duTE5ZcUNxMkw1WVRqVW5mYmI3YWhvRk02LVIwa01pb2VEWExYa2dMVzhsd3hOSFpaYWZXMHBkeUdBSXhIMllqeUZkdHl0bThMY3MtWlZGQTVFUGxjRkc4elRR?oc=5</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
@@ -834,49 +834,49 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gli ETF più popolari del trimestre - Morningstar</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sat, 28 Jun 2025 23:59:51 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbDFGNWY3WS1FT0tmdkZMc1k4QlVLUmhQOExzcE45T1VmWDBYWGZOeENJVGFhMS16ajcydFNaUFdwRkNxZ183X1AxNkh0NGR0RGdyYzN0Q196bndPVDRNWVBKQi1JZ1oyaDJHWTA2Qlc1ZmxaamI1Tm1sN2tRWnloTmN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,67 +894,67 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
@@ -981,57 +981,57 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 06:15:19 GMT</t>
+          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1041,22 +1041,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CIO Weekly: What Happens If No One Hikes? - Neuberger Berman</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 01:41:45 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNMHNmWVc0YmhqQnBtcHBJaTZwN3dIdFB2Yld5ZGdHRExVaGs2VWRtQnY2a2NxaGxGR3V2dGZOc29ySWVJSTJhUDdyRy1YdGh3NnFiV3l2a0RPSmJOMllITXdOQTVaQ3pTTFRRR3A5VU5uSTcwX2xid25FOGx3dG5OcVR1M0o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1074,24 +1074,24 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>From refuge to coexistence: why gold and equities no longer take turns - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1111,47 +1111,47 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IMF: global growth resilient (for now) to tensions and tariffs. Artificial intelligence uncertain - Il Sole 24 ORE</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
+          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWmVJdjR6ZWdNR3IwNnFwRUNnQllhRFhCYXR2WXMzWDhBdXUtMVc4djM1X2h4QldNRUFMeXB2VUp5WFN1ZlFVUTU3SHpqdG12Yl9sRm9XSzlJSkM2bkdfUndiamRUSjMzMFZINDIySk5OSUJrbzNfUUN6SlY1ZWVwb29tc2QteDdNUVdpd3VGa3RQNEpTV19mXy01ODBsd3dkNlExVEpKZUd6SDhfUWRGRTl3MkdXNThHWlZvWmVOOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1194,94 +1194,94 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Stock market: shares open higher following Wall Street’s rally, with Milan immediately above the 52,000 mark - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOUlRaVpqSHBQaUFiUVpWSHAzd09ZUkQ5QXZjYVRuMTVQUGtkcEpHS1hHbkNRVlotNHRwQ1BrQUE2ZENBOVRHcTZqb3B2T3pwcnVQdXdrekthNVo5UThBei1fV3dWZjlEbncyajUwRlMzV0pEZlhVVm5ia0JEczRPZkFINUpQbWE0US1ES01Qc29LZTNfUGs3U1JDcjZOaDJJQ2pDSmZGOGpBWWVtRldTamtVUVFiZThsTHhrX0loVGhOcmhTeDlsVQ?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1291,117 +1291,117 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 06:15:19 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CIO Weekly: What Happens If No One Hikes? - Neuberger Berman</t>
+          <t>Stock Market Today January 27: Nasdaq Deep in the Red, Nvidia Collapses. Milan Looks to Risk, Mps Still Down - LIVE - firstonline.info</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>firstonline.info</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 01:41:45 GMT</t>
+          <t>Mon, 27 Jan 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNMHNmWVc0YmhqQnBtcHBJaTZwN3dIdFB2Yld5ZGdHRExVaGs2VWRtQnY2a2NxaGxGR3V2dGZOc29ySWVJSTJhUDdyRy1YdGh3NnFiV3l2a0RPSmJOMllITXdOQTVaQ3pTTFRRR3A5VU5uSTcwX2xid25FOGx3dG5OcVR1M0o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxORS15UkozMVZ6anBOcUNGNmx0NHNWODdsLUpDYVVUS2FsbXdrcW1meVd0RWxsck5zd0VNODl3Wko2VXZLZG0tWUxySldWRC12T0I3UlMzdld5dVM2eW5uT1NTX3kyVkVnTE8weVBCLWZ2bWswSThLeUpLRXdSWnlQUThKNHNTX0ZuVUN6OUFfd3laOHRfSXJ2OE01bldvdlRTY1FfN3BROWpvSmxUcVFFaDFDWU9oa2hjTnltS2tjaWg3eDZLLWNRSFh5OC10eXg0ZHR6N3laOUkxeGlSOHRrNnd4VQ?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>From refuge to coexistence: why gold and equities no longer take turns - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOb05vOVZNSlZfNlMxcktmYWhIQmlzMmJEekFIVmtWRFYxaHVRRFVXbFd2LWZuakM4cEdPSFBGNlp0SDVySUp3QXZ4TUVOTUI4VEQzY3VLdmVQcFFDMlpiZDhjcHI1WDZvc1lBTUdkM1VzSVZ2N1A5Rl92TDhCbDVCakVXak53NjRvakVMZ1pHeDNqdzN6N0JoWHc0ZzJHT0ZQS1Jxazl2Q0V5aXplaGJN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1434,34 +1434,34 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IMF: global growth resilient (for now) to tensions and tariffs. Artificial intelligence uncertain - Il Sole 24 ORE</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWmVJdjR6ZWdNR3IwNnFwRUNnQllhRFhCYXR2WXMzWDhBdXUtMVc4djM1X2h4QldNRUFMeXB2VUp5WFN1ZlFVUTU3SHpqdG12Yl9sRm9XSzlJSkM2bkdfUndiamRUSjMzMFZINDIySk5OSUJrbzNfUUN6SlY1ZWVwb29tc2QteDdNUVdpd3VGa3RQNEpTV19mXy01ODBsd3dkNlExVEpKZUd6SDhfUWRGRTl3MkdXNThHWlZvWmVOOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1494,49 +1494,49 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Rapporto annuale BCE 2020 - European Central Bank</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>European Central Bank</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Mon, 25 Mar 2024 21:19:24 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSC1tOUJ0R1JjS1ZPVVdTUWZfN1pWYk8xb1hRYlViTmo5VXVObWdUTHFoMWVGNzJvWUlaaHU0VmQtU0NEY3ZhWTRtbEpjT0Zha2VOUmFBWE5kQmcxSWZPalF0ZFdnVWtYWWM0NG9IS1FlTVllbXFFMGVfT29hQTlXU1NtMjR3NmxqVWZZUHpWdThXcVVmYVFFYWR2R1pILTRCaHhrb1NtT0s?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1554,34 +1554,34 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1591,57 +1591,57 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stock market: shares open higher following Wall Street’s rally, with Milan immediately above the 52,000 mark - Il Sole 24 ORE</t>
+          <t>US inflation falls to 2.5% in August, below estimates. Stock markets fall - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,57 +1651,57 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 10 Sep 2024 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOUlRaVpqSHBQaUFiUVpWSHAzd09ZUkQ5QXZjYVRuMTVQUGtkcEpHS1hHbkNRVlotNHRwQ1BrQUE2ZENBOVRHcTZqb3B2T3pwcnVQdXdrekthNVo5UThBei1fV3dWZjlEbncyajUwRlMzV0pEZlhVVm5ia0JEczRPZkFINUpQbWE0US1ES01Qc29LZTNfUGs3U1JDcjZOaDJJQ2pDSmZGOGpBWWVtRldTamtVUVFiZThsTHhrX0loVGhOcmhTeDlsVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNak10cEV1ZG9kY1QwdlF5dHkxMEg4MURfeV9Gb291V0t3ZzhJMnhzMVNVOXBaSkdwbnlldURYa0JxcTJrUHdpdk8tM0tONW51Um1UdDNDNlc0VUNCd3RxLWFZVlBkZ01jQXIxaVNWVUhyRE55aWN5VGJaUl9GUGoyVjBjaG44Zw?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potrebbe pesare su azionario europeo</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Stock markets: Europe takes a breather after a record half-year; Milan down 0.15 per cent. Wall Street in the red - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,450 +1711,30 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmw4QWxUeXBEWHprbkxrd0RNX3ZUTkJmXzc4TkF5LTEtYVl4T1JOQkdBV2QwTndjWHJFOWt2MGNpdEFCQklpTldPTHlzWlY2M1JOOGJubWc2cUlRdlRtT2Y0UnA1WHUtalo4U2ZNSkdtbk4xajY0R1NRX19CV1VRWFhDNUlJRUhfemc?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe pesare su azionario europeo</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:28+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>IE000DWG3DP6</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fineco AM Passive Underlyings 8</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Multi asset crescita</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Stock Market Today January 27: Nasdaq Deep in the Red, Nvidia Collapses. Milan Looks to Risk, Mps Still Down - LIVE - firstonline.info</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>firstonline.info</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Mon, 27 Jan 2025 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxORS15UkozMVZ6anBOcUNGNmx0NHNWODdsLUpDYVVUS2FsbXdrcW1meVd0RWxsck5zd0VNODl3Wko2VXZLZG0tWUxySldWRC12T0I3UlMzdld5dVM2eW5uT1NTX3kyVkVnTE8weVBCLWZ2bWswSThLeUpLRXdSWnlQUThKNHNTX0ZuVUN6OUFfd3laOHRfSXJ2OE01bldvdlRTY1FfN3BROWpvSmxUcVFFaDFDWU9oa2hjTnltS2tjaWg3eDZLLWNRSFh5OC10eXg0ZHR6N3laOUkxeGlSOHRrNnd4VQ?oc=5</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Attenzione / pressione negativa</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-09-02T21:11:28+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>IE000DWG3DP6</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Fineco AM Passive Underlyings 8</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Multi asset crescita</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Potenzialmente favorevole</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Potenziale supporto di breve periodo</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2026-09-02T21:11:28+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2026-09-02T21:11:28+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>2026-09-02T21:11:28+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ECB and Eurozone central banks: we need a single market with the same deposit guarantees - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPc3dNeE5QRkFBM0Vmck44N2tJcGJialpMY3VFUF9FLTJDYVl4WUxFem9zTEZXejlZWVN1aHR2aDdLRFJwc2NpbTdtSzUyODF6X3B4ZERLLTVVZ0VfbFhNMWRqczRJbjVZWXlGamxwbWhNY0FHVUVwRHVjZ2FRaFJsZ3l2Y1Z6SnBLd245blhNVmxZU0VoMFFFSWZpaVFiQjVQb1pUM2U3YVBDRVU5ZXdzRnlxRQ?oc=5</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2026-09-02T21:11:28+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Stock market: Europe weighed down by banks and tech; MPS surge fails to lift Milan (-0.8%) - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Wed, 19 Aug 2026 16:06:01 GMT</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxObzAybVNtTDczVENhSUFxb29RbExsTlp5TVc3dmhxdUR1MUhtb3ZvVk44VUpfTlQ3bGlPaV9LLTFEZ3dFd0xLLWtJeGZsWlhUMEcwVFc2V3ViX2k5RENaTlNwNEVPYkFCUnc1OTRET1NtaFNWc1FpQTFmcFBlSllReTZINVdzXzVtMFhrWk04UElVZEc2SC1wMlhMM3hieFVSU3VyUGpadkJDNzgyOWRYbnh6dllyQklXRGY5RExOQ003MHQ5YUhBWndzc0pHd1NCR2c?oc=5</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-09-02T21:11:28+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>EU stock exchanges and Wall Street in the red on inflation fears, Milan -2% - Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Il Sole 24 ORE</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQMjhXUGRDb1BzeGlrNG9vX3JwaVVoVGR4WGFnQUM5N2pnVERfbTZUTGRmemVpdkZFcWFJNlVfVHk5OVAzaUIxbjdObUZxaDJWdjkwM3UzdUltVDZjZDlqZ0lleTdfekhDTHl3WkFlZVZXSGtMLTVhRi12MDNqOVZseGdrNlVvUG13?oc=5</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Attenzione / pressione negativa</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Potrebbe pesare su azionario europeo</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2026-09-02T21:11:28+00:00</t>
+          <t>2026-09-03T21:10:48+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Interview with Peter Elston - wallstreetitalia.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>wallstreetitalia.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -681,22 +681,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net</t>
+          <t>3 titoli ad alto dividendo per il mese di settembre - Morningstar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+          <t>Fri, 05 Sep 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNUTRONmdsT0RIc2NWbkxSdmlOLVl3cmxZYXV5SnNweF9lMUszQ3VxVFRoa3UyV2F2WWM1SlVzVFV6OHZkazlBZmlPUVBVcF9EdksyZC1SOHg5OTJnNHpYNlRQSkxtdlZXRks1ckhzYmw0cFpVaF8tUGZaUE51WkhobnVmRmxMdUtEZENqVXdTTmxGZVBxeU9V?oc=5</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -741,22 +741,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3 titoli ad alto dividendo per il mese di settembre - Morningstar</t>
+          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fri, 05 Sep 2025 07:00:00 GMT</t>
+          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNUTRONmdsT0RIc2NWbkxSdmlOLVl3cmxZYXV5SnNweF9lMUszQ3VxVFRoa3UyV2F2WWM1SlVzVFV6OHZkazlBZmlPUVBVcF9EdksyZC1SOHg5OTJnNHpYNlRQSkxtdlZXRks1ckhzYmw0cFpVaF8tUGZaUE51WkhobnVmRmxMdUtEZENqVXdTTmxGZVBxeU9V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1014,24 +1014,24 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1041,22 +1041,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>TMGM Daily Market Breakfast: 2 September 2026 - tmgm.com</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Wed, 02 Sep 2026 23:51:27 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNmRhZHdsTERYZWd3c2tMN05Ga3YzNHhGUHRoYnZabEU1cndSWUVKci10NkFkVFFVLUx4WGtkUzVmNHJJa09OZS1hUzc0WWlic25oNU5rRkNWUXhNNHlYOW5obkJLeHBZZWU5RzJfTTNaMHVWS0ZkYVF1R0lvYzY1UQ?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1074,24 +1074,24 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>EU stock markets in the red amid tensions over the Strait of Hormuz and bond yields; Milan brings up the rear (-1.1 per cent); Wall Street down - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1111,30 +1111,30 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Mon, 17 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzFlQTA0YlVmUXIwTEU2Um5rVHE3cTBpeWM4TmttcFpkc0R1VWk0X2pmcE11NUgtNFRRM1JfVkpBcUVWOVFDdGloQTJIU1FFT18zSHllbjVnYlU2QWoydjU1SVQyRnFYUlNFYlMwVHEtNkVWa28zcVI4bUxvTzNhQ0lORmhrX2FsN0lFOWh5QmdJRVdsMVlaTE1Nb09Hb1dnb3BLX0V6dmVUX09DRG9hSms1elBhOGlyMHNr?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,22 +1161,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1194,34 +1194,34 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stock market: shares open higher following Wall Street’s rally, with Milan immediately above the 52,000 mark - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOUlRaVpqSHBQaUFiUVpWSHAzd09ZUkQ5QXZjYVRuMTVQUGtkcEpHS1hHbkNRVlotNHRwQ1BrQUE2ZENBOVRHcTZqb3B2T3pwcnVQdXdrekthNVo5UThBei1fV3dWZjlEbncyajUwRlMzV0pEZlhVVm5ia0JEczRPZkFINUpQbWE0US1ES01Qc29LZTNfUGs3U1JDcjZOaDJJQ2pDSmZGOGpBWWVtRldTamtVUVFiZThsTHhrX0loVGhOcmhTeDlsVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1254,34 +1254,34 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1314,94 +1314,94 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock Market Today January 27: Nasdaq Deep in the Red, Nvidia Collapses. Milan Looks to Risk, Mps Still Down - LIVE - firstonline.info</t>
+          <t>TMGM Daily Market Breakfast: 2 September 2026 - tmgm.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>firstonline.info</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mon, 27 Jan 2025 08:00:00 GMT</t>
+          <t>Wed, 02 Sep 2026 23:51:27 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxORS15UkozMVZ6anBOcUNGNmx0NHNWODdsLUpDYVVUS2FsbXdrcW1meVd0RWxsck5zd0VNODl3Wko2VXZLZG0tWUxySldWRC12T0I3UlMzdld5dVM2eW5uT1NTX3kyVkVnTE8weVBCLWZ2bWswSThLeUpLRXdSWnlQUThKNHNTX0ZuVUN6OUFfd3laOHRfSXJ2OE01bldvdlRTY1FfN3BROWpvSmxUcVFFaDFDWU9oa2hjTnltS2tjaWg3eDZLLWNRSFh5OC10eXg0ZHR6N3laOUkxeGlSOHRrNnd4VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNmRhZHdsTERYZWd3c2tMN05Ga3YzNHhGUHRoYnZabEU1cndSWUVKci10NkFkVFFVLUx4WGtkUzVmNHJJa09OZS1hUzc0WWlic25oNU5rRkNWUXhNNHlYOW5obkJLeHBZZWU5RzJfTTNaMHVWS0ZkYVF1R0lvYzY1UQ?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>EU stock markets in the red amid tensions over the Strait of Hormuz and bond yields; Milan brings up the rear (-1.1 per cent); Wall Street down - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Mon, 17 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzFlQTA0YlVmUXIwTEU2Um5rVHE3cTBpeWM4TmttcFpkc0R1VWk0X2pmcE11NUgtNFRRM1JfVkpBcUVWOVFDdGloQTJIU1FFT18zSHllbjVnYlU2QWoydjU1SVQyRnFYUlNFYlMwVHEtNkVWa28zcVI4bUxvTzNhQ0lORmhrX2FsN0lFOWh5QmdJRVdsMVlaTE1Nb09Hb1dnb3BLX0V6dmVUX09DRG9hSms1elBhOGlyMHNr?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1434,34 +1434,34 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LU0261952682</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fidelity Euro 50 Index Fund</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1476,172 +1476,172 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LU0261952682</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity Euro 50 Index Fund</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapporto annuale BCE 2020 - European Central Bank</t>
+          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>European Central Bank</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mon, 25 Mar 2024 21:19:24 GMT</t>
+          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSC1tOUJ0R1JjS1ZPVVdTUWZfN1pWYk8xb1hRYlViTmo5VXVObWdUTHFoMWVGNzJvWUlaaHU0VmQtU0NEY3ZhWTRtbEpjT0Zha2VOUmFBWE5kQmcxSWZPalF0ZFdnVWtYWWM0NG9IS1FlTVllbXFFMGVfT29hQTlXU1NtMjR3NmxqVWZZUHpWdThXcVVmYVFFYWR2R1pILTRCaHhrb1NtT0s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LU0261952682</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fidelity Euro 50 Index Fund</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Stock Market Today January 27: Nasdaq Deep in the Red, Nvidia Collapses. Milan Looks to Risk, Mps Still Down - LIVE - firstonline.info</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>firstonline.info</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 27 Jan 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxORS15UkozMVZ6anBOcUNGNmx0NHNWODdsLUpDYVVUS2FsbXdrcW1meVd0RWxsck5zd0VNODl3Wko2VXZLZG0tWUxySldWRC12T0I3UlMzdld5dVM2eW5uT1NTX3kyVkVnTE8weVBCLWZ2bWswSThLeUpLRXdSWnlQUThKNHNTX0ZuVUN6OUFfd3laOHRfSXJ2OE01bldvdlRTY1FfN3BROWpvSmxUcVFFaDFDWU9oa2hjTnltS2tjaWg3eDZLLWNRSFh5OC10eXg0ZHR6N3laOUkxeGlSOHRrNnd4VQ?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LU0261952682</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity Euro 50 Index Fund</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>US inflation falls to 2.5% in August, below estimates. Stock markets fall - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,30 +1651,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tue, 10 Sep 2024 07:00:00 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNak10cEV1ZG9kY1QwdlF5dHkxMEg4MURfeV9Gb291V0t3ZzhJMnhzMVNVOXBaSkdwbnlldURYa0JxcTJrUHdpdk8tM0tONW51Um1UdDNDNlc0VUNCd3RxLWFZVlBkZ01jQXIxaVNWVUhyRE55aWN5VGJaUl9GUGoyVjBjaG44Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Potrebbe pesare su azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stock markets: Europe takes a breather after a record half-year; Milan down 0.15 per cent. Wall Street in the red - Il Sole 24 ORE</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,30 +1711,270 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmw4QWxUeXBEWHprbkxrd0RNX3ZUTkJmXzc4TkF5LTEtYVl4T1JOQkdBV2QwTndjWHJFOWt2MGNpdEFCQklpTldPTHlzWlY2M1JOOGJubWc2cUlRdlRtT2Y0UnA1WHUtalo4U2ZNSkdtbk4xajY0R1NRX19CV1VRWFhDNUlJRUhfemc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Neutro / da monitorare</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Da monitorare: impatto non evidente</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-04T20:53:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>eurozone equities ECB inflation Europe stocks</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ECB: Geopolitical instability and high energy prices threaten growth in the eurozone - Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNQ3IxaGlHZ0tZdVdyRFlwMHJvYVpFeUFEdURaamVGMW5ySHlpOVFhelpsNWFjUk9yZFRlSWktQkY3ZFh0MlRocXc4NFdJSHEzX0syWFZpSlUweUczWkpNNkNabE9HQTRMUzdqSHF3YU5xOWdCcWdpN3VmZWgxWkY1ZnVyYnVBRy04MlZfd0ZQaXRvckNxWWYwazJNeGhNSnFxNTdOY2ZYdEdUMWg5S0lMZ28tNzdZWnhDYTBYNFlaMGhZVGpBcFNLR3FrTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Potenzialmente favorevole</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Potrebbe supportare azionario europeo</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-04T20:53:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>eurozone equities ECB inflation Europe stocks</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Neutro / da monitorare</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Da monitorare: impatto non evidente</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-04T20:53:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>eurozone equities ECB inflation Europe stocks</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tough US economy reassures stock exchanges, Wall Street best month since 2020 - Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQeGR3M0hXeEVSMjZjaDU4WDJPZklSTUtGRmtiY1dqNFVza3RMTDBSNU56Nlo1bVRRUEMyNm9WME9YNUJ6NkhicWZ2ZEZjZmtBZ1hHVnl5Sk5iTFBRN2tGSHFsLXBlZkFkdDNNYjNfMW03cHBwdU5ySWxXaEJrcVFQeHhlZndIY0JMdVdXTmxBa1VnNUpYVnpxRWVBRHJDOWdZLV9PME1ackxDZi1IWnlrNWZR?oc=5</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Neutro / da monitorare</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Da monitorare: impatto non evidente</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-04T20:53:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>eurozone equities ECB inflation Europe stocks</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>US inflation falls to 2.5% in August, below estimates. Stock markets fall - Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tue, 10 Sep 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNak10cEV1ZG9kY1QwdlF5dHkxMEg4MURfeV9Gb291V0t3ZzhJMnhzMVNVOXBaSkdwbnlldURYa0JxcTJrUHdpdk8tM0tONW51Um1UdDNDNlc0VUNCd3RxLWFZVlBkZ01jQXIxaVNWVUhyRE55aWN5VGJaUl9GUGoyVjBjaG44Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>-1</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Attenzione / pressione negativa</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Potrebbe pesare su azionario europeo</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-09-03T21:10:48+00:00</t>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-04T20:53:44+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,27 +481,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IE00BD2PJG29</t>
+          <t>IE0003YRHWF4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FAM MSCI Emerging Markets Index Fund</t>
+          <t>Sustainable Future Connectivity FAM Fund</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>emerging markets China India equities dollar rates</t>
+          <t>technology cloud connectivity artificial intelligence semiconductors Nasdaq rates</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The new hierarchies of the currency market - Il Sole 24 ORE</t>
+          <t>Stm flies in the stock market for Amazon Web Services agreement - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,12 +511,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thu, 21 May 2026 07:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5ENUZmYV9HQzdUV0Z2S2RjQ3FsUm9xWkkxT19xRXVuS1dILU1NUGRJQTU5cXJ6S296ajVIRUlseThsMG41SFI0ZkNNdUh6ZG1pem50RUh2cHVxaFNQcXMycmY1b2dwNDZwSEZNSHkwbjdYVm1QZjVTWk1xUlpRdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNbkpXTUplRjFHbXhCWVhqNUlDX0tZUXFfUW1ld19TeVppTXpYWHFYWFFEcFI1VXg5UFdJQ0xLbDBnbkwyY25XbWk4bGdiclFkaERLa0xNZEdCZUJVb2RLMHRESFBMN2wxdV9tYWlSOGVNSmhOY3hQVlRrczNiaXJaY1A2a0VYOVNpelZqdnFrUlp3SDNOQ0NxSFpxOGg?oc=5</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - wallstreetitalia.com</t>
+          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>wallstreetitalia.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
+          <t>Sat, 05 Oct 2024 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPNVNWZkg1OXdPY01La05BQnBCa0JVU29KY0xocVM3aktBTEJTaFgzbHljME8tcVJCb09lV2VQd0pZblE1ZnA4Q2F5ZVVjZFVxbGk1U0xiMktUNVlvVWdTX1Ywa2FMRUx6UnpLS2lfbmFGNjNyVEtIc2tIRVAwVFRaRXFwYmxOLTBrdGJr?oc=5</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -621,22 +621,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dividend Aristocrats: migliori azioni a dividendo crescente 2026 - Investing.com</t>
+          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
+          <t>Mon, 11 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB0TktUb19nYXlxR0duTE5ZcUNxMkw1WVRqVW5mYmI3YWhvRk02LVIwa01pb2VEWExYa2dMVzhsd3hOSFpaYWZXMHBkeUdBSXhIMllqeUZkdHl0bThMY3MtWlZGQTVFUGxjRkc4elRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -681,22 +681,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3 titoli ad alto dividendo per il mese di settembre - Morningstar</t>
+          <t>Dividend Aristocrats: migliori azioni a dividendo crescente 2026 - Investing.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fri, 05 Sep 2025 07:00:00 GMT</t>
+          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNUTRONmdsT0RIc2NWbkxSdmlOLVl3cmxZYXV5SnNweF9lMUszQ3VxVFRoa3UyV2F2WWM1SlVzVFV6OHZkazlBZmlPUVBVcF9EdksyZC1SOHg5OTJnNHpYNlRQSkxtdlZXRks1ckhzYmw0cFpVaF8tUGZaUE51WkhobnVmRmxMdUtEZENqVXdTTmxGZVBxeU9V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB0TktUb19nYXlxR0duTE5ZcUNxMkw1WVRqVW5mYmI3YWhvRk02LVIwa01pb2VEWExYa2dMVzhsd3hOSFpaYWZXMHBkeUdBSXhIMllqeUZkdHl0bThMY3MtWlZGQTVFUGxjRkc4elRR?oc=5</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -741,22 +741,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
+          <t>Capital One Announces Quarterly Dividend - 01net</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -834,49 +834,49 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>ETF JEGP | JPM Global Equity Premium Income Active UCITS ETF - USD (dist) quotazione - Investing.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Mon, 18 Dec 2023 08:07:52 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE8xd2tXUWdWMlVXSm43OGltTWRyaC10N1pTN21XSS1tbkhjZ1poODJQWVpYMzhfckY2Z1o3OUhZV09zYld1N0ZfYXdJVzE0V2tpVzEw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -931,30 +931,30 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -981,40 +981,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,22 +1041,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TMGM Daily Market Breakfast: 2 September 2026 - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 23:51:27 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNmRhZHdsTERYZWd3c2tMN05Ga3YzNHhGUHRoYnZabEU1cndSWUVKci10NkFkVFFVLUx4WGtkUzVmNHJJa09OZS1hUzc0WWlic25oNU5rRkNWUXhNNHlYOW5obkJLeHBZZWU5RzJfTTNaMHVWS0ZkYVF1R0lvYzY1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EU stock markets in the red amid tensions over the Strait of Hormuz and bond yields; Milan brings up the rear (-1.1 per cent); Wall Street down - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1111,47 +1111,47 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzFlQTA0YlVmUXIwTEU2Um5rVHE3cTBpeWM4TmttcFpkc0R1VWk0X2pmcE11NUgtNFRRM1JfVkpBcUVWOVFDdGloQTJIU1FFT18zSHllbjVnYlU2QWoydjU1SVQyRnFYUlNFYlMwVHEtNkVWa28zcVI4bUxvTzNhQ0lORmhrX2FsN0lFOWh5QmdJRVdsMVlaTE1Nb09Hb1dnb3BLX0V6dmVUX09DRG9hSms1elBhOGlyMHNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1161,40 +1161,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1231,30 +1231,30 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TMGM Daily Market Breakfast: 2 September 2026 - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 23:51:27 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNmRhZHdsTERYZWd3c2tMN05Ga3YzNHhGUHRoYnZabEU1cndSWUVKci10NkFkVFFVLUx4WGtkUzVmNHJJa09OZS1hUzc0WWlic25oNU5rRkNWUXhNNHlYOW5obkJLeHBZZWU5RzJfTTNaMHVWS0ZkYVF1R0lvYzY1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EU stock markets in the red amid tensions over the Strait of Hormuz and bond yields; Milan brings up the rear (-1.1 per cent); Wall Street down - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1411,72 +1411,72 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzFlQTA0YlVmUXIwTEU2Um5rVHE3cTBpeWM4TmttcFpkc0R1VWk0X2pmcE11NUgtNFRRM1JfVkpBcUVWOVFDdGloQTJIU1FFT18zSHllbjVnYlU2QWoydjU1SVQyRnFYUlNFYlMwVHEtNkVWa28zcVI4bUxvTzNhQ0lORmhrX2FsN0lFOWh5QmdJRVdsMVlaTE1Nb09Hb1dnb3BLX0V6dmVUX09DRG9hSms1elBhOGlyMHNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1531,30 +1531,30 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,40 +1581,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stock Market Today January 27: Nasdaq Deep in the Red, Nvidia Collapses. Milan Looks to Risk, Mps Still Down - LIVE - firstonline.info</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>firstonline.info</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mon, 27 Jan 2025 08:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxORS15UkozMVZ6anBOcUNGNmx0NHNWODdsLUpDYVVUS2FsbXdrcW1meVd0RWxsck5zd0VNODl3Wko2VXZLZG0tWUxySldWRC12T0I3UlMzdld5dVM2eW5uT1NTX3kyVkVnTE8weVBCLWZ2bWswSThLeUpLRXdSWnlQUThKNHNTX0ZuVUN6OUFfd3laOHRfSXJ2OE01bldvdlRTY1FfN3BROWpvSmxUcVFFaDFDWU9oa2hjTnltS2tjaWg3eDZLLWNRSFh5OC10eXg0ZHR6N3laOUkxeGlSOHRrNnd4VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,57 +1651,57 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LU0261952682</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Euro 50 Index Fund</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ECB: Geopolitical instability and high energy prices threaten growth in the eurozone - Il Sole 24 ORE</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1771,30 +1771,30 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNQ3IxaGlHZ0tZdVdyRFlwMHJvYVpFeUFEdURaamVGMW5ySHlpOVFhelpsNWFjUk9yZFRlSWktQkY3ZFh0MlRocXc4NFdJSHEzX0syWFZpSlUweUczWkpNNkNabE9HQTRMUzdqSHF3YU5xOWdCcWdpN3VmZWgxWkY1ZnVyYnVBRy04MlZfd0ZQaXRvckNxWWYwazJNeGhNSnFxNTdOY2ZYdEdUMWg5S0lMZ28tNzdZWnhDYTBYNFlaMGhZVGpBcFNLR3FrTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tough US economy reassures stock exchanges, Wall Street best month since 2020 - Il Sole 24 ORE</t>
+          <t>ECB and Eurozone central banks: we need a single market with the same deposit guarantees - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:00:00 GMT</t>
+          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQeGR3M0hXeEVSMjZjaDU4WDJPZklSTUtGRmtiY1dqNFVza3RMTDBSNU56Nlo1bVRRUEMyNm9WME9YNUJ6NkhicWZ2ZEZjZmtBZ1hHVnl5Sk5iTFBRN2tGSHFsLXBlZkFkdDNNYjNfMW03cHBwdU5ySWxXaEJrcVFQeHhlZndIY0JMdVdXTmxBa1VnNUpYVnpxRWVBRHJDOWdZLV9PME1ackxDZi1IWnlrNWZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPc3dNeE5QRkFBM0Vmck44N2tJcGJialpMY3VFUF9FLTJDYVl4WUxFem9zTEZXejlZWVN1aHR2aDdLRFJwc2NpbTdtSzUyODF6X3B4ZERLLTVVZ0VfbFhNMWRqczRJbjVZWXlGamxwbWhNY0FHVUVwRHVjZ2FRaFJsZ3l2Y1Z6SnBLd245blhNVmxZU0VoMFFFSWZpaVFiQjVQb1pUM2U3YVBDRVU5ZXdzRnlxRQ?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,40 +1941,100 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>US inflation falls to 2.5% in August, below estimates. Stock markets fall - Il Sole 24 ORE</t>
+          <t>Rapporto annuale BCE 2020 - European Central Bank</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>European Central Bank</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tue, 10 Sep 2024 07:00:00 GMT</t>
+          <t>Mon, 25 Mar 2024 21:19:24 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNak10cEV1ZG9kY1QwdlF5dHkxMEg4MURfeV9Gb291V0t3ZzhJMnhzMVNVOXBaSkdwbnlldURYa0JxcTJrUHdpdk8tM0tONW51Um1UdDNDNlc0VUNCd3RxLWFZVlBkZ01jQXIxaVNWVUhyRE55aWN5VGJaUl9GUGoyVjBjaG44Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSC1tOUJ0R1JjS1ZPVVdTUWZfN1pWYk8xb1hRYlViTmo5VXVObWdUTHFoMWVGNzJvWUlaaHU0VmQtU0NEY3ZhWTRtbEpjT0Zha2VOUmFBWE5kQmcxSWZPalF0ZFdnVWtYWWM0NG9IS1FlTVllbXFFMGVfT29hQTlXU1NtMjR3NmxqVWZZUHpWdThXcVVmYVFFYWR2R1pILTRCaHhrb1NtT0s?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Potrebbe pesare su azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:44+00:00</t>
+          <t>2026-09-07T11:21:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>eurozone equities ECB inflation Europe stocks</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>La Stampa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Neutro / da monitorare</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Da monitorare: impatto non evidente</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-07T11:21:43+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -834,49 +834,49 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ETF JEGP | JPM Global Equity Premium Income Active UCITS ETF - USD (dist) quotazione - Investing.com</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mon, 18 Dec 2023 08:07:52 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE8xd2tXUWdWMlVXSm43OGltTWRyaC10N1pTN21XSS1tbkhjZ1poODJQWVpYMzhfckY2Z1o3OUhZV09zYld1N0ZfYXdJVzE0V2tpVzEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -921,40 +921,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -981,40 +981,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1051,30 +1051,30 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,57 +1101,57 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>TMGM Daily Market Breakfast: 2 September 2026 - tmgm.com</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 02 Sep 2026 23:51:27 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNmRhZHdsTERYZWd3c2tMN05Ga3YzNHhGUHRoYnZabEU1cndSWUVKci10NkFkVFFVLUx4WGtkUzVmNHJJa09OZS1hUzc0WWlic25oNU5rRkNWUXhNNHlYOW5obkJLeHBZZWU5RzJfTTNaMHVWS0ZkYVF1R0lvYzY1UQ?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1161,40 +1161,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,40 +1221,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1351,30 +1351,30 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,100 +1401,100 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>TMGM Daily Market Breakfast: 2 September 2026 - tmgm.com</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 02 Sep 2026 23:51:27 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNmRhZHdsTERYZWd3c2tMN05Ga3YzNHhGUHRoYnZabEU1cndSWUVKci10NkFkVFFVLUx4WGtkUzVmNHJJa09OZS1hUzc0WWlic25oNU5rRkNWUXhNNHlYOW5obkJLeHBZZWU5RzJfTTNaMHVWS0ZkYVF1R0lvYzY1UQ?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,57 +1651,57 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>LU0261952682</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fidelity Euro 50 Index Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>eurozone equities ECB inflation Europe stocks</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>EU stock markets: Frankfurt brings up the rear following the AfD’s victory. Milan holds its ground thanks to Lottomatica - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,30 +1711,30 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Mon, 07 Sep 2026 05:26:11 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQcVQ4WEpRWDNkTEtrc2tPbWJraUUyQ2xTazBPTWZrcTVpYkVjWFNzT3NuSjJTR3RwMnF4Q1pPc1EyTUd1VmJMWGNxNVhXbm5NZ2l6bUFrMG5SSDFGMnAwUW42Q0pQSWNkelNQdFUwSGlRejA5SVRhc2JnaHpoUExOWjJZVS1GNlYxNFhv?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,22 +1821,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECB and Eurozone central banks: we need a single market with the same deposit guarantees - Il Sole 24 ORE</t>
+          <t>EU stock markets lose momentum in the final hours; Milan closes unchanged - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
+          <t>Wed, 12 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPc3dNeE5QRkFBM0Vmck44N2tJcGJialpMY3VFUF9FLTJDYVl4WUxFem9zTEZXejlZWVN1aHR2aDdLRFJwc2NpbTdtSzUyODF6X3B4ZERLLTVVZ0VfbFhNMWRqczRJbjVZWXlGamxwbWhNY0FHVUVwRHVjZ2FRaFJsZ3l2Y1Z6SnBLd245blhNVmxZU0VoMFFFSWZpaVFiQjVQb1pUM2U3YVBDRVU5ZXdzRnlxRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNSDAxbWRoZHRYNC14MERrVXdTcmY5ZVRXaG04WmhVdXdvOVh3TXh1T3d1eVY3VktIYzBkbUg1LVd4TlQ4bXZldWNETlZjNjl2M1NvOXBYdS1UWmJFOXpzTU1XN0VQQnRYX0pUSFU1VXNlZGNJb0w1S3g5SF80cUV3UUwycmtta05wcU5qc1VFVUxWOHhwWG5Hdl9GOA?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,22 +1941,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rapporto annuale BCE 2020 - European Central Bank</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>European Central Bank</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mon, 25 Mar 2024 21:19:24 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSC1tOUJ0R1JjS1ZPVVdTUWZfN1pWYk8xb1hRYlViTmo5VXVObWdUTHFoMWVGNzJvWUlaaHU0VmQtU0NEY3ZhWTRtbEpjT0Zha2VOUmFBWE5kQmcxSWZPalF0ZFdnVWtYWWM0NG9IS1FlTVllbXFFMGVfT29hQTlXU1NtMjR3NmxqVWZZUHpWdThXcVVmYVFFYWR2R1pILTRCaHhrb1NtT0s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1974,67 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:43+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LU0261952682</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Fidelity Euro 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>La Stampa</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Neutro / da monitorare</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Da monitorare: impatto non evidente</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2026-09-07T11:21:43+00:00</t>
+          <t>2026-09-07T17:54:29+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,12 +501,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stm flies in the stock market for Amazon Web Services agreement - Il Sole 24 ORE</t>
+          <t>Stm flies in the stock market for Amazon Web Services agreement - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
+          <t>'Time to return to investing in emerging markets' - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,49 +594,49 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE00BD2PJG29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>FAM MSCI Emerging Markets Index Fund</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>emerging markets China India equities dollar rates</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:00:00 GMT</t>
+          <t>Wed, 30 Jan 2019 04:06:23 GMT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9JbElUOWlvYjU5SkxWRTFnOFZkVlpHUnhXbWhpcUo2NVR2VEctWEhfeVkySnlqOVpsQ2o0cWpZQUJqQm9wcGJaOWhVcDAyNFdfTkx5M09NNU9sUGF1OXVyUF9ES254YVdrVTBaelZB?oc=5</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -681,22 +681,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dividend Aristocrats: migliori azioni a dividendo crescente 2026 - Investing.com</t>
+          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
+          <t>Mon, 11 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB0TktUb19nYXlxR0duTE5ZcUNxMkw1WVRqVW5mYmI3YWhvRk02LVIwa01pb2VEWExYa2dMVzhsd3hOSFpaYWZXMHBkeUdBSXhIMllqeUZkdHl0bThMY3MtWlZGQTVFUGxjRkc4elRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -741,22 +741,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net</t>
+          <t>Dividend Aristocrats: migliori azioni a dividendo crescente 2026 - Investing.com</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB0TktUb19nYXlxR0duTE5ZcUNxMkw1WVRqVW5mYmI3YWhvRk02LVIwa01pb2VEWExYa2dMVzhsd3hOSFpaYWZXMHBkeUdBSXhIMllqeUZkdHl0bThMY3MtWlZGQTVFUGxjRkc4elRR?oc=5</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -801,22 +801,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
+          <t>Capital One Announces Quarterly Dividend - 01net</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,49 +834,49 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -921,40 +921,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -981,40 +981,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,40 +1041,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,57 +1101,57 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TMGM Daily Market Breakfast: 2 September 2026 - tmgm.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 23:51:27 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNmRhZHdsTERYZWd3c2tMN05Ga3YzNHhGUHRoYnZabEU1cndSWUVKci10NkFkVFFVLUx4WGtkUzVmNHJJa09OZS1hUzc0WWlic25oNU5rRkNWUXhNNHlYOW5obkJLeHBZZWU5RzJfTTNaMHVWS0ZkYVF1R0lvYzY1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1161,40 +1161,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,40 +1221,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,40 +1341,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,100 +1401,100 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TMGM Daily Market Breakfast: 2 September 2026 - tmgm.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 23:51:27 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNmRhZHdsTERYZWd3c2tMN05Ga3YzNHhGUHRoYnZabEU1cndSWUVKci10NkFkVFFVLUx4WGtkUzVmNHJJa09OZS1hUzc0WWlic25oNU5rRkNWUXhNNHlYOW5obkJLeHBZZWU5RzJfTTNaMHVWS0ZkYVF1R0lvYzY1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1521,40 +1521,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,40 +1581,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,22 +1641,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1674,67 +1674,67 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LU0261952682</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Euro 50 Index Fund</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EU stock markets: Frankfurt brings up the rear following the AfD’s victory. Milan holds its ground thanks to Lottomatica - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 05:26:11 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQcVQ4WEpRWDNkTEtrc2tPbWJraUUyQ2xTazBPTWZrcTVpYkVjWFNzT3NuSjJTR3RwMnF4Q1pPc1EyTUd1VmJMWGNxNVhXbm5NZ2l6bUFrMG5SSDFGMnAwUW42Q0pQSWNkelNQdFUwSGlRejA5SVRhc2JnaHpoUExOWjJZVS1GNlYxNFhv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,40 +1761,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>EU stock markets: Frankfurt brings up the rear following the AfD’s victory. Milan holds its ground thanks to Lottomatica - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 07 Sep 2026 05:26:11 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQcVQ4WEpRWDNkTEtrc2tPbWJraUUyQ2xTazBPTWZrcTVpYkVjWFNzT3NuSjJTR3RwMnF4Q1pPc1EyTUd1VmJMWGNxNVhXbm5NZ2l6bUFrMG5SSDFGMnAwUW42Q0pQSWNkelNQdFUwSGlRejA5SVRhc2JnaHpoUExOWjJZVS1GNlYxNFhv?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,22 +1821,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,22 +1881,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EU stock markets lose momentum in the final hours; Milan closes unchanged - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNSDAxbWRoZHRYNC14MERrVXdTcmY5ZVRXaG04WmhVdXdvOVh3TXh1T3d1eVY3VktIYzBkbUg1LVd4TlQ4bXZldWNETlZjNjl2M1NvOXBYdS1UWmJFOXpzTU1XN0VQQnRYX0pUSFU1VXNlZGNJb0w1S3g5SF80cUV3UUwycmtta05wcU5qc1VFVUxWOHhwWG5Hdl9GOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,22 +1941,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>EU stock markets lose momentum in the final hours; Milan closes unchanged - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 12 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNSDAxbWRoZHRYNC14MERrVXdTcmY5ZVRXaG04WmhVdXdvOVh3TXh1T3d1eVY3VktIYzBkbUg1LVd4TlQ4bXZldWNETlZjNjl2M1NvOXBYdS1UWmJFOXpzTU1XN0VQQnRYX0pUSFU1VXNlZGNJb0w1S3g5SF80cUV3UUwycmtta05wcU5qc1VFVUxWOHhwWG5Hdl9GOA?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1974,7 +1974,67 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:29+00:00</t>
+          <t>2026-09-07T21:45:25+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>eurozone equities ECB inflation Europe stocks</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - en.ilsole24ore.com</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>en.ilsole24ore.com</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Neutro / da monitorare</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Da monitorare: impatto non evidente</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-07T21:45:25+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -501,12 +501,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stm flies in the stock market for Amazon Web Services agreement - en.ilsole24ore.com</t>
+          <t>Stm flies in the stock market for Amazon Web Services agreement - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>'Time to return to investing in emerging markets' - en.ilsole24ore.com</t>
+          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - en.ilsole24ore.com</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,40 +1101,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,40 +1161,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - en.ilsole24ore.com</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,40 +1401,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,40 +1461,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - en.ilsole24ore.com</t>
+          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - en.ilsole24ore.com</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - en.ilsole24ore.com</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - en.ilsole24ore.com</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,40 +1761,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EU stock markets: Frankfurt brings up the rear following the AfD’s victory. Milan holds its ground thanks to Lottomatica - en.ilsole24ore.com</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 05:26:11 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQcVQ4WEpRWDNkTEtrc2tPbWJraUUyQ2xTazBPTWZrcTVpYkVjWFNzT3NuSjJTR3RwMnF4Q1pPc1EyTUd1VmJMWGNxNVhXbm5NZ2l6bUFrMG5SSDFGMnAwUW42Q0pQSWNkelNQdFUwSGlRejA5SVRhc2JnaHpoUExOWjJZVS1GNlYxNFhv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,22 +1821,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - en.ilsole24ore.com</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,40 +1881,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>ECB: Geopolitical instability and high energy prices threaten growth in the eurozone - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Thu, 06 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNQ3IxaGlHZ0tZdVdyRFlwMHJvYVpFeUFEdURaamVGMW5ySHlpOVFhelpsNWFjUk9yZFRlSWktQkY3ZFh0MlRocXc4NFdJSHEzX0syWFZpSlUweUczWkpNNkNabE9HQTRMUzdqSHF3YU5xOWdCcWdpN3VmZWgxWkY1ZnVyYnVBRy04MlZfd0ZQaXRvckNxWWYwazJNeGhNSnFxNTdOY2ZYdEdUMWg5S0lMZ28tNzdZWnhDYTBYNFlaMGhZVGpBcFNLR3FrTQ?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EU stock markets lose momentum in the final hours; Milan closes unchanged - en.ilsole24ore.com</t>
+          <t>EU stock markets lose momentum in the final hours; Milan closes unchanged - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - en.ilsole24ore.com</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:25+00:00</t>
+          <t>2026-09-08T12:16:50+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
+          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,49 +894,49 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -981,40 +981,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,40 +1041,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,40 +1101,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,57 +1161,57 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1231,30 +1231,30 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,40 +1341,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,40 +1401,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,67 +1461,67 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1591,30 +1591,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,30 +1651,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1734,34 +1734,34 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LU0261952682</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity Euro 50 Index Fund</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,22 +1821,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,40 +1881,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECB: Geopolitical instability and high energy prices threaten growth in the eurozone - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNQ3IxaGlHZ0tZdVdyRFlwMHJvYVpFeUFEdURaamVGMW5ySHlpOVFhelpsNWFjUk9yZFRlSWktQkY3ZFh0MlRocXc4NFdJSHEzX0syWFZpSlUweUczWkpNNkNabE9HQTRMUzdqSHF3YU5xOWdCcWdpN3VmZWgxWkY1ZnVyYnVBRy04MlZfd0ZQaXRvckNxWWYwazJNeGhNSnFxNTdOY2ZYdEdUMWg5S0lMZ28tNzdZWnhDYTBYNFlaMGhZVGpBcFNLR3FrTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EU stock markets lose momentum in the final hours; Milan closes unchanged - Il Sole 24 ORE</t>
+          <t>ECB: Geopolitical instability and high energy prices threaten growth in the eurozone - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1951,30 +1951,30 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 07:00:00 GMT</t>
+          <t>Thu, 06 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNSDAxbWRoZHRYNC14MERrVXdTcmY5ZVRXaG04WmhVdXdvOVh3TXh1T3d1eVY3VktIYzBkbUg1LVd4TlQ4bXZldWNETlZjNjl2M1NvOXBYdS1UWmJFOXpzTU1XN0VQQnRYX0pUSFU1VXNlZGNJb0w1S3g5SF80cUV3UUwycmtta05wcU5qc1VFVUxWOHhwWG5Hdl9GOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNQ3IxaGlHZ0tZdVdyRFlwMHJvYVpFeUFEdURaamVGMW5ySHlpOVFhelpsNWFjUk9yZFRlSWktQkY3ZFh0MlRocXc4NFdJSHEzX0syWFZpSlUweUczWkpNNkNabE9HQTRMUzdqSHF3YU5xOWdCcWdpN3VmZWgxWkY1ZnVyYnVBRy04MlZfd0ZQaXRvckNxWWYwazJNeGhNSnFxNTdOY2ZYdEdUMWg5S0lMZ28tNzdZWnhDYTBYNFlaMGhZVGpBcFNLR3FrTQ?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,67 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:50+00:00</t>
+          <t>2026-09-08T16:51:27+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>eurozone equities ECB inflation Europe stocks</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Stock markets: renewed US-Iran tensions send markets into turmoil. Milan holds its ground as crude oil prices surge - Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sun, 30 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNYjMwYWtNTlZFQ05IUzNvY0ZJS2wtYXE2QTU4MUh2MWNWbUFKOEdEdWo5SUlheTVpNmZVMkZ1LUpEYXZreWJZdHRrTmRZY2twcnZCSUZCNm9SS010OFNxdHc2a3daUmoxQ3RwcUJTVU10VlBKd3BWd1EwT1BjVlFQNDA2VnUxWkU2?oc=5</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Potenzialmente favorevole</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Potrebbe supportare azionario europeo</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-08T16:51:27+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SAR prezzo e grafico azione — NYSE:SAR - TradingView</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - it.tradingview.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>it.tradingview.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sun, 23 Jul 2017 20:34:53 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1qRTlETFJRX1Y5WmZCTkI3ZDd5dDdPTlBsY2dLdExIOU1raTJQa0Y0N2V5NjJGS3liMDRfbTJ4MTZtOGFlWDNNRGYyaVJxYjFIQW5OVzFJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,49 +894,49 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LU0981915779</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Core Dividend</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dividend globale</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>global dividend equities income rates</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -981,40 +981,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,40 +1041,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1111,30 +1111,30 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1194,24 +1194,24 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1231,30 +1231,30 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,40 +1341,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1411,30 +1411,30 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1494,34 +1494,34 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1531,30 +1531,30 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNRXpPazFNeTl3R1kwMFVqbkVLNzk3OUliU3FCUE4ySlZBcmFPVDJWVzgydEphZlAwY0tiNW1nWjl2U1pkYUFxNFhEeVVTOEdMamNpRXZPaEF5T2VmbXltLVBjTnpQcW96U2JGcmI0M3FxczNSbVNsMEQ5cHZpY01vb0E4SVRwN2VK?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:27+00:00</t>
+          <t>2026-09-08T21:22:48+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Interview with Peter Elston - wallstreetitalia.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>wallstreetitalia.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -681,22 +681,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
+          <t>I migliori fondi azionari globali orientati al reddito - global.morningstar.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>global.morningstar.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:00:00 GMT</t>
+          <t>Wed, 22 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPWWYza0tjaXdYVmg5Z0hHb3FaLXp2TXBJMkhTUllmLVZJa2lRb3VIaGxVYTM0QXdDTTBQcEQzUnNCUE1CNUk0dHl0U1FwdU5iMXNTOGxGVXVjMFlYMWtSajYzS3BHVUcyVndzVmdHcjdjQ0dRVnZjeGhDZjJ3eC0xTFczMVRtS3Z3MS1ILWV2RUptM0ZOaGFOTGtB?oc=5</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -741,22 +741,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dividend Aristocrats: migliori azioni a dividendo crescente 2026 - Investing.com</t>
+          <t>Capital One Announces Quarterly Dividend - 01net</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB0TktUb19nYXlxR0duTE5ZcUNxMkw1WVRqVW5mYmI3YWhvRk02LVIwa01pb2VEWExYa2dMVzhsd3hOSFpaYWZXMHBkeUdBSXhIMllqeUZkdHl0bThMY3MtWlZGQTVFUGxjRkc4elRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -801,22 +801,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net</t>
+          <t>Dividend Aristocrats: migliori azioni a dividendo crescente 2026 - Investing.com</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1oODBjVTdORThLLVV5a0VSOTMycnRCZWlWR25YZlVvX2RmUXdveS0xQjUxSG1YQ1FFVC1GSjR4QkNSc01tX21BTFVBcnBoSDFKMzNrNVk1SEhqS1BzYlo3XzhzOHI1TnBncXpjQWpyNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB0TktUb19nYXlxR0duTE5ZcUNxMkw1WVRqVW5mYmI3YWhvRk02LVIwa01pb2VEWExYa2dMVzhsd3hOSFpaYWZXMHBkeUdBSXhIMllqeUZkdHl0bThMY3MtWlZGQTVFUGxjRkc4elRR?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - it.tradingview.com</t>
+          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - global.morningstar.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>it.tradingview.com</t>
+          <t>global.morningstar.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Mon, 11 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -921,40 +921,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -981,40 +981,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,40 +1101,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,40 +1161,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>EU stock markets in the red amid tensions over the Strait of Hormuz and bond yields; Milan brings up the rear (-1.1 per cent); Wall Street down - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Mon, 17 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzFlQTA0YlVmUXIwTEU2Um5rVHE3cTBpeWM4TmttcFpkc0R1VWk0X2pmcE11NUgtNFRRM1JfVkpBcUVWOVFDdGloQTJIU1FFT18zSHllbjVnYlU2QWoydjU1SVQyRnFYUlNFYlMwVHEtNkVWa28zcVI4bUxvTzNhQ0lORmhrX2FsN0lFOWh5QmdJRVdsMVlaTE1Nb09Hb1dnb3BLX0V6dmVUX09DRG9hSms1elBhOGlyMHNr?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,40 +1221,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Why the stock markets cannot ignore the bond market turmoil - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:20:21 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQU9hbVNwazI2eFkwMjhzYl9wY0VUaFFwdC1LaFJZUGc4Y0lKMFgwZVNUbnlQV1lSaTVQaVBIdjhvLWREaUZzMG1vLUtiQkNSa20tNUtPVVZyVlRwV2xTRU0tSnQ3c2ZvSVpWUHNCeWhZaE91VkpTZFpzaHhQWFN3bktiZ3Eyb3ZqeFJhN0dxbjRvc0xwZTFjYURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,40 +1401,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,40 +1461,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>EU stock markets in the red amid tensions over the Strait of Hormuz and bond yields; Milan brings up the rear (-1.1 per cent); Wall Street down - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Mon, 17 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzFlQTA0YlVmUXIwTEU2Um5rVHE3cTBpeWM4TmttcFpkc0R1VWk0X2pmcE11NUgtNFRRM1JfVkpBcUVWOVFDdGloQTJIU1FFT18zSHllbjVnYlU2QWoydjU1SVQyRnFYUlNFYlMwVHEtNkVWa28zcVI4bUxvTzNhQ0lORmhrX2FsN0lFOWh5QmdJRVdsMVlaTE1Nb09Hb1dnb3BLX0V6dmVUX09DRG9hSms1elBhOGlyMHNr?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>European stock markets are set for a weak start ahead of tomorrow’s ECB meeting; Milan holds steady. Gas prices above 78 euros - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1831,30 +1831,30 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 09 Sep 2026 06:44:56 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOS25YaF9kOVZiYXc3Wi16U1Ffdkdjc1ZpOW56WGtLczVreDBBQktxaUFEQW1EWlZfeHFrZmFOOFlKQWhLRUJ6U29iZE9STTBNcjZUQmRxNXVkeHA2QTRxZEpiZktJM25Nd2Nrd0tYWEthbW9rZUFEakhRUFhwWXY0bmJDWUt2Yl9JanJlTDNnWE5KdHpOQXdOazdwV3dnbHB4ajRFTFM3bVA0VS1nVUNaRFZUU2ZzOWcxdC1nN3JEMUFQLUsybGc?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe pesare su azionario europeo</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,22 +1881,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,40 +1941,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ECB: Geopolitical instability and high energy prices threaten growth in the eurozone - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNQ3IxaGlHZ0tZdVdyRFlwMHJvYVpFeUFEdURaamVGMW5ySHlpOVFhelpsNWFjUk9yZFRlSWktQkY3ZFh0MlRocXc4NFdJSHEzX0syWFZpSlUweUczWkpNNkNabE9HQTRMUzdqSHF3YU5xOWdCcWdpN3VmZWgxWkY1ZnVyYnVBRy04MlZfd0ZQaXRvckNxWWYwazJNeGhNSnFxNTdOY2ZYdEdUMWg5S0lMZ28tNzdZWnhDYTBYNFlaMGhZVGpBcFNLR3FrTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,40 +2001,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stock markets: renewed US-Iran tensions send markets into turmoil. Milan holds its ground as crude oil prices surge - Il Sole 24 ORE</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2071,30 +2071,30 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNYjMwYWtNTlZFQ05IUzNvY0ZJS2wtYXE2QTU4MUh2MWNWbUFKOEdEdWo5SUlheTVpNmZVMkZ1LUpEYXZreWJZdHRrTmRZY2twcnZCSUZCNm9SS010OFNxdHc2a3daUmoxQ3RwcUJTVU10VlBKd3BWd1EwT1BjVlFQNDA2VnUxWkU2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:48+00:00</t>
+          <t>2026-09-09T10:34:35+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - wallstreetitalia.com</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>wallstreetitalia.com</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I migliori fondi azionari globali orientati al reddito - global.morningstar.com</t>
+          <t>I migliori fondi azionari globali orientati al reddito - Morningstar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>global.morningstar.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net</t>
+          <t>Capital One Announces Quarterly Dividend - 01net.it</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>01net.it</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -801,22 +801,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dividend Aristocrats: migliori azioni a dividendo crescente 2026 - Investing.com</t>
+          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 07:00:00 GMT</t>
+          <t>Mon, 11 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB0TktUb19nYXlxR0duTE5ZcUNxMkw1WVRqVW5mYmI3YWhvRk02LVIwa01pb2VEWExYa2dMVzhsd3hOSFpaYWZXMHBkeUdBSXhIMllqeUZkdHl0bThMY3MtWlZGQTVFUGxjRkc4elRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - global.morningstar.com</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>global.morningstar.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stock market: Wall Street rebounds as Treasury yields fall. Moderna soars on the back of its melanoma vaccine - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1591,30 +1591,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZ2JBV0JBY2lhU3k1TGNzc1l2MXdsWmFsdlNiRW53S2hTTWxSb1ZBSTlkQVFHVXp4dUp4YUx1QUxoa3FzSy1GMG5Cc2dHSVRSdU1EYkdIZXpKS0JqaUYwMXl3NXdnS0lySWwxdXE3ZlpDdUg2REpwWlI5V2xtLUZZY29hQ2VrRlUwekwzNzRxMHVTY1BHSXNxRElZaHl4QWpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,30 +1651,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>European stock markets are set for a weak start ahead of tomorrow’s ECB meeting; Milan holds steady. Gas prices above 78 euros - Il Sole 24 ORE</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1831,30 +1831,30 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 06:44:56 GMT</t>
+          <t>Tue, 08 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOS25YaF9kOVZiYXc3Wi16U1Ffdkdjc1ZpOW56WGtLczVreDBBQktxaUFEQW1EWlZfeHFrZmFOOFlKQWhLRUJ6U29iZE9STTBNcjZUQmRxNXVkeHA2QTRxZEpiZktJM25Nd2Nrd0tYWEthbW9rZUFEakhRUFhwWXY0bmJDWUt2Yl9JanJlTDNnWE5KdHpOQXdOazdwV3dnbHB4ajRFTFM3bVA0VS1nVUNaRFZUU2ZzOWcxdC1nN3JEMUFQLUsybGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOeC1LTzN2WUwxbTVYM19qY0J3VlJZYkU3MVJ5NU0yaS1odGFuVnNIY0hLS1Z1SWhWMlJIdHpVZ1BwNVhpbkVCMUY4NjJVSTJybHhiVGtaWmk5Rkhvdm5zSk9nUVVLN0YyRzdVMUN5QUFRRS1POENGdFMzVFg5THJzcHlmZnZOQUtXdXdZdDNVb1d0Q1NFWWlOemZoWFdyYVBNT1VGR2tPSFJsQjJLaE9BeHhvMm1yWGZQ?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Potrebbe pesare su azionario europeo</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,22 +1881,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,40 +1941,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,40 +2001,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:35+00:00</t>
+          <t>2026-09-09T17:10:32+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net.it</t>
+          <t>Capital One Announces Quarterly Dividend - 01net</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01net.it</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
+          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1831,30 +1831,30 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 07:00:00 GMT</t>
+          <t>Wed, 09 Sep 2026 05:43:19 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOeC1LTzN2WUwxbTVYM19qY0J3VlJZYkU3MVJ5NU0yaS1odGFuVnNIY0hLS1Z1SWhWMlJIdHpVZ1BwNVhpbkVCMUY4NjJVSTJybHhiVGtaWmk5Rkhvdm5zSk9nUVVLN0YyRzdVMUN5QUFRRS1POENGdFMzVFg5THJzcHlmZnZOQUtXdXdZdDNVb1d0Q1NFWWlOemZoWFdyYVBNT1VGR2tPSFJsQjJLaE9BeHhvMm1yWGZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSHRqc0s0UU8yZjJzXzJCU3luQzRPRE14RnlVOWZCY3JMcHVlb2NObktDamE1X2lsbDFzcmZZTnpzTWY4TmxIeWRYb05NU2tNY3hwVUt6RWFHMXYtX3pJeHJqOFNjRE1LNHRDbnptdWNsRXN6YTVDZ3JBeDQ5NUcwT3pELVNURlF1cDVVTmdvT0pKZE1tTm1QamVGbmZTUW82NEZKOXVZWHhyQ0hoOS1MN21Bdw?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,40 +1881,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Tue, 08 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdXprcEtqNHVyNjRUa0ota3piVXRqSUhRb2RiaC0zRUMzMW1JRnQwRFJPU0EyVkNzeTZqLWV5aENIOUVYNXZIRTlMekJwUHMwZnlqWmVLVnpLa0hER0NxZnVQQmNrRXBtRHhVMllaQzhwU3FTVlRyODcwVzJrRzVabWh3ekZCTTJOR1I3b3pFN09GVUxEYUFMM2lJaEhpVlduZzdjamY5YXNUei1xdHZpWlc2V3pMTEl3VnpRbQ?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,40 +1941,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,40 +2001,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:32+00:00</t>
+          <t>2026-09-09T19:16:36+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdXprcEtqNHVyNjRUa0ota3piVXRqSUhRb2RiaC0zRUMzMW1JRnQwRFJPU0EyVkNzeTZqLWV5aENIOUVYNXZIRTlMekJwUHMwZnlqWmVLVnpLa0hER0NxZnVQQmNrRXBtRHhVMllaQzhwU3FTVlRyODcwVzJrRzVabWh3ekZCTTJOR1I3b3pFN09GVUxEYUFMM2lJaEhpVlduZzdjamY5YXNUei1xdHZpWlc2V3pMTEl3VnpRbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOeC1LTzN2WUwxbTVYM19qY0J3VlJZYkU3MVJ5NU0yaS1odGFuVnNIY0hLS1Z1SWhWMlJIdHpVZ1BwNVhpbkVCMUY4NjJVSTJybHhiVGtaWmk5Rkhvdm5zSk9nUVVLN0YyRzdVMUN5QUFRRS1POENGdFMzVFg5THJzcHlmZnZOQUtXdXdZdDNVb1d0Q1NFWWlOemZoWFdyYVBNT1VGR2tPSFJsQjJLaE9BeHhvMm1yWGZQ?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:36+00:00</t>
+          <t>2026-09-09T21:44:06+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,12 +501,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stm flies in the stock market for Amazon Web Services agreement - Il Sole 24 ORE</t>
+          <t>Stm flies in the stock market for Amazon Web Services agreement - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
+          <t>'Time to return to investing in emerging markets' - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I migliori fondi azionari globali orientati al reddito - Morningstar</t>
+          <t>I migliori fondi azionari globali orientati al reddito - global.morningstar.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>global.morningstar.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
+          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - global.morningstar.com</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>global.morningstar.com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
+          <t>I migliori 3 fondi azionari income - global.morningstar.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>global.morningstar.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Thu, 22 May 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5yMVBmdkdBZkZCV1dIU0x4dmpQVVp6U28tcW9aSG1ZeW9pak1CN09ZLXdTOENVNnV3SnBWUGg5Y0plTzhLS0hmeGVzeUhaTGpwQlh6emZiX0d3VUt1MXhLZmFJU1BNeEFZN09tMF9mVVdqOW5jRjN0WE5NZjFPZW8?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,67 +894,67 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IE0005TOUMC7</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 7</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Multi asset</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>global equities bonds inflation central banks</t>
+          <t>global dividend equities income rates</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -981,40 +981,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Gold: Inflation data key catalyst – TD Securities - tmgm.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 09 Sep 2026 18:17:56 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZW5USVloaXo1bEtJNlRqNXJqdnlRSE1FQzJrSmQ1dmd5bmQ5QTFkbGdIYnZjNTFRemtLdGc0dkYyUzdNOHVZSFBQaThjRE5lS2JuR2p4SFppczJVcGN4ODlyRzFXX0Z2T1NrZ2tBeHdqM2pMd1VlT0wtTEtLUEpmNVYyVnlzNktxWmZIbXUyV1ZoczlBNmd1aGV5NldDNVdHT3pmNmVlVi1EV00xa0kyTVh3?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,40 +1041,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1111,16 +1111,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,22 +1161,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EU stock markets in the red amid tensions over the Strait of Hormuz and bond yields; Milan brings up the rear (-1.1 per cent); Wall Street down - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 07:00:00 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzFlQTA0YlVmUXIwTEU2Um5rVHE3cTBpeWM4TmttcFpkc0R1VWk0X2pmcE11NUgtNFRRM1JfVkpBcUVWOVFDdGloQTJIU1FFT18zSHllbjVnYlU2QWoydjU1SVQyRnFYUlNFYlMwVHEtNkVWa28zcVI4bUxvTzNhQ0lORmhrX2FsN0lFOWh5QmdJRVdsMVlaTE1Nb09Hb1dnb3BLX0V6dmVUX09DRG9hSms1elBhOGlyMHNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1194,24 +1194,24 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IE000KTYLDC4</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 6</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Multi asset prudente</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1221,40 +1221,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>A record-breaking week for European stock markets, but doubts remain over bonds - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Gold: Inflation data key catalyst – TD Securities - tmgm.com</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Wed, 09 Sep 2026 18:17:56 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZW5USVloaXo1bEtJNlRqNXJqdnlRSE1FQzJrSmQ1dmd5bmQ5QTFkbGdIYnZjNTFRemtLdGc0dkYyUzdNOHVZSFBQaThjRE5lS2JuR2p4SFppczJVcGN4ODlyRzFXX0Z2T1NrZ2tBeHdqM2pMd1VlT0wtTEtLUEpmNVYyVnlzNktxWmZIbXUyV1ZoczlBNmd1aGV5NldDNVdHT3pmNmVlVi1EV00xa0kyTVh3?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,40 +1341,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1411,16 +1411,16 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,22 +1461,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EU stock markets in the red amid tensions over the Strait of Hormuz and bond yields; Milan brings up the rear (-1.1 per cent); Wall Street down - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 07:00:00 GMT</t>
+          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzFlQTA0YlVmUXIwTEU2Um5rVHE3cTBpeWM4TmttcFpkc0R1VWk0X2pmcE11NUgtNFRRM1JfVkpBcUVWOVFDdGloQTJIU1FFT18zSHllbjVnYlU2QWoydjU1SVQyRnFYUlNFYlMwVHEtNkVWa28zcVI4bUxvTzNhQ0lORmhrX2FsN0lFOWh5QmdJRVdsMVlaTE1Nb09Hb1dnb3BLX0V6dmVUX09DRG9hSms1elBhOGlyMHNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1494,49 +1494,49 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IE000DWG3DP6</t>
+          <t>IE000KTYLDC4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fineco AM Passive Underlyings 8</t>
+          <t>Fineco AM Passive Underlyings 6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Multi asset crescita</t>
+          <t>Multi asset prudente</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>global equities growth stocks central banks Nasdaq</t>
+          <t>global equities bonds inflation central banks</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - Il Sole 24 ORE</t>
+          <t>A record-breaking week for European stock markets, but doubts remain over bonds - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
+          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNRXpPazFNeTl3R1kwMFVqbkVLNzk3OUliU3FCUE4ySlZBcmFPVDJWVzgydEphZlAwY0tiNW1nWjl2U1pkYUFxNFhEeVVTOEdMamNpRXZPaEF5T2VmbXltLVBjTnpQcW96U2JGcmI0M3FxczNSbVNsMEQ5cHZpY01vb0E4SVRwN2VK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,40 +1581,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNRXpPazFNeTl3R1kwMFVqbkVLNzk3OUliU3FCUE4ySlZBcmFPVDJWVzgydEphZlAwY0tiNW1nWjl2U1pkYUFxNFhEeVVTOEdMamNpRXZPaEF5T2VmbXltLVBjTnpQcW96U2JGcmI0M3FxczNSbVNsMEQ5cHZpY01vb0E4SVRwN2VK?oc=5</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,40 +1641,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,22 +1701,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1794,49 +1794,49 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LU0261952682</t>
+          <t>IE000DWG3DP6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity Euro 50 Index Fund</t>
+          <t>Fineco AM Passive Underlyings 8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Multi asset crescita</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>eurozone equities ECB inflation Europe stocks</t>
+          <t>global equities growth stocks central banks Nasdaq</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 05:43:19 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSHRqc0s0UU8yZjJzXzJCU3luQzRPRE14RnlVOWZCY3JMcHVlb2NObktDamE1X2lsbDFzcmZZTnpzTWY4TmxIeWRYb05NU2tNY3hwVUt6RWFHMXYtX3pJeHJqOFNjRE1LNHRDbnptdWNsRXN6YTVDZ3JBeDQ5NUcwT3pELVNURlF1cDVVTmdvT0pKZE1tTm1QamVGbmZTUW82NEZKOXVZWHhyQ0hoOS1MN21Bdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,40 +1881,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
+          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 07:00:00 GMT</t>
+          <t>Wed, 09 Sep 2026 05:43:19 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOeC1LTzN2WUwxbTVYM19qY0J3VlJZYkU3MVJ5NU0yaS1odGFuVnNIY0hLS1Z1SWhWMlJIdHpVZ1BwNVhpbkVCMUY4NjJVSTJybHhiVGtaWmk5Rkhvdm5zSk9nUVVLN0YyRzdVMUN5QUFRRS1POENGdFMzVFg5THJzcHlmZnZOQUtXdXdZdDNVb1d0Q1NFWWlOemZoWFdyYVBNT1VGR2tPSFJsQjJLaE9BeHhvMm1yWGZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSHRqc0s0UU8yZjJzXzJCU3luQzRPRE14RnlVOWZCY3JMcHVlb2NObktDamE1X2lsbDFzcmZZTnpzTWY4TmxIeWRYb05NU2tNY3hwVUt6RWFHMXYtX3pJeHJqOFNjRE1LNHRDbnptdWNsRXN6YTVDZ3JBeDQ5NUcwT3pELVNURlF1cDVVTmdvT0pKZE1tTm1QamVGbmZTUW82NEZKOXVZWHhyQ0hoOS1MN21Bdw?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,40 +1941,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Tue, 08 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdXprcEtqNHVyNjRUa0ota3piVXRqSUhRb2RiaC0zRUMzMW1JRnQwRFJPU0EyVkNzeTZqLWV5aENIOUVYNXZIRTlMekJwUHMwZnlqWmVLVnpLa0hER0NxZnVQQmNrRXBtRHhVMllaQzhwU3FTVlRyODcwVzJrRzVabWh3ekZCTTJOR1I3b3pFN09GVUxEYUFMM2lJaEhpVlduZzdjamY5YXNUei1xdHZpWlc2V3pMTEl3VnpRbQ?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,40 +2001,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,40 +2061,100 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Forex Today: ECB rate decision, US producer inflation data to lift volatility - tmgm.com</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Thu, 10 Sep 2026 09:08:25 GMT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUTdVWG1kQWtfRGlqcmhTQ092VmlTYnVOcmoyUDIzdVFMd0VIUEtidUR1eFFYN1hWRmxtWWR2dzNCVXppVHNucThZWHNVM3M4MjV4VEJOVDIxLWJOMnBSTHFSUUlINHVrNXBHOHBqQzFtU2cwWGh0REtkSHF4b2RNcnRlMFlPNEU4M08wQ1N0SmFHclZFRWlNUzB5UTNja1JPRnVKOGFoUVF6bktEcVNNMTBiODd1UGNOZ2ZVYnN2cEJ6TXJUZTNqLUtQeHp1ZHZxMDlJcDY3OXI?oc=5</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Attenzione / pressione negativa</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Potrebbe pesare su azionario europeo</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-10T12:15:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>eurozone equities ECB inflation Europe stocks</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - en.ilsole24ore.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>en.ilsole24ore.com</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Neutro / da monitorare</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-09-09T21:44:06+00:00</t>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-10T12:15:34+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -501,12 +501,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stm flies in the stock market for Amazon Web Services agreement - en.ilsole24ore.com</t>
+          <t>Stm flies in the stock market for Amazon Web Services agreement - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>'Time to return to investing in emerging markets' - en.ilsole24ore.com</t>
+          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Interview with Peter Elston - wallstreetitalia.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>wallstreetitalia.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I migliori fondi azionari globali orientati al reddito - global.morningstar.com</t>
+          <t>I migliori fondi azionari globali orientati al reddito - Morningstar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>global.morningstar.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net</t>
+          <t>Capital One Announces Quarterly Dividend - 01net.it</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>01net.it</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - global.morningstar.com</t>
+          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>global.morningstar.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I migliori 3 fondi azionari income - global.morningstar.com</t>
+          <t>I migliori 3 fondi azionari income - Morningstar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>global.morningstar.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,40 +1221,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A record-breaking week for European stock markets, but doubts remain over bonds - en.ilsole24ore.com</t>
+          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1521,40 +1521,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A record-breaking week for European stock markets, but doubts remain over bonds - en.ilsole24ore.com</t>
+          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 07:00:00 GMT</t>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVVNGanI4Q1B4dWYwMFdoSkN4VWZUSnF0TVFRMG9FbG1YNTk4Q0QyZ0R6XzVpT1RrNDBfb29rekFfbzBnWDNlV25LU3pEQjlYVFplX3JMWE1SVkRLWE1lcWlCQUFlTVF3RmF3RFF0OWNIVlJGN29YS1h1RC1RNXRUZFlkaGRDbHBaVkZOMkNNVXYwclRYb2NsdnJwUFg2TzlHYy1xVnYtYUJUVk1BOS1yT0xEbG9wc3J4MkpQUnQ3RTUtVFZhVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - en.ilsole24ore.com</t>
+          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - en.ilsole24ore.com</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - en.ilsole24ore.com</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,17 +1761,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - en.ilsole24ore.com</t>
+          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 29 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - en.ilsole24ore.com</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - en.ilsole24ore.com</t>
+          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - en.ilsole24ore.com</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Forex Today: ECB rate decision, US producer inflation data to lift volatility - tmgm.com</t>
+          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2071,30 +2071,30 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thu, 10 Sep 2026 09:08:25 GMT</t>
+          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUTdVWG1kQWtfRGlqcmhTQ092VmlTYnVOcmoyUDIzdVFMd0VIUEtidUR1eFFYN1hWRmxtWWR2dzNCVXppVHNucThZWHNVM3M4MjV4VEJOVDIxLWJOMnBSTHFSUUlINHVrNXBHOHBqQzFtU2cwWGh0REtkSHF4b2RNcnRlMFlPNEU4M08wQ1N0SmFHclZFRWlNUzB5UTNja1JPRnVKOGFoUVF6bktEcVNNMTBiODd1UGNOZ2ZVYnN2cEJ6TXJUZTNqLUtQeHp1ZHZxMDlJcDY3OXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Potrebbe pesare su azionario europeo</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2121,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - en.ilsole24ore.com</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:34+00:00</t>
+          <t>2026-09-10T14:30:23+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - wallstreetitalia.com</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>wallstreetitalia.com</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net.it</t>
+          <t>Capital One Announces Quarterly Dividend - 01net</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01net.it</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1051,30 +1051,30 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1171,30 +1171,30 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1351,30 +1351,30 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1471,30 +1471,30 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 05:25:22 GMT</t>
+          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdXprcEtqNHVyNjRUa0ota3piVXRqSUhRb2RiaC0zRUMzMW1JRnQwRFJPU0EyVkNzeTZqLWV5aENIOUVYNXZIRTlMekJwUHMwZnlqWmVLVnpLa0hER0NxZnVQQmNrRXBtRHhVMllaQzhwU3FTVlRyODcwVzJrRzVabWh3ekZCTTJOR1I3b3pFN09GVUxEYUFMM2lJaEhpVlduZzdjamY5YXNUei1xdHZpWlc2V3pMTEl3VnpRbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOeC1LTzN2WUwxbTVYM19qY0J3VlJZYkU3MVJ5NU0yaS1odGFuVnNIY0hLS1Z1SWhWMlJIdHpVZ1BwNVhpbkVCMUY4NjJVSTJybHhiVGtaWmk5Rkhvdm5zSk9nUVVLN0YyRzdVMUN5QUFRRS1POENGdFMzVFg5THJzcHlmZnZOQUtXdXdZdDNVb1d0Q1NFWWlOemZoWFdyYVBNT1VGR2tPSFJsQjJLaE9BeHhvMm1yWGZQ?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:23+00:00</t>
+          <t>2026-09-10T17:00:17+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -501,12 +501,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stm flies in the stock market for Amazon Web Services agreement - Il Sole 24 ORE</t>
+          <t>Stm flies in the stock market for Amazon Web Services agreement - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
+          <t>'Time to return to investing in emerging markets' - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1521,26 +1521,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - Il Sole 24 ORE</t>
+          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
+          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
+          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,22 +2001,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>en.ilsole24ore.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,40 +2061,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2121,40 +2121,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:17+00:00</t>
+          <t>2026-09-10T19:07:50+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -501,12 +501,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stm flies in the stock market for Amazon Web Services agreement - en.ilsole24ore.com</t>
+          <t>Stm flies in the stock market for Amazon Web Services agreement - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>'Time to return to investing in emerging markets' - en.ilsole24ore.com</t>
+          <t>'Time to return to investing in emerging markets' - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - en.ilsole24ore.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - en.ilsole24ore.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - en.ilsole24ore.com</t>
+          <t>Stock markets welcome the US-Iran deal; Milan hits a new record, led by banks. Wall Street ends the day mixed - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - en.ilsole24ore.com</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - en.ilsole24ore.com</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - en.ilsole24ore.com</t>
+          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - en.ilsole24ore.com</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - en.ilsole24ore.com</t>
+          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,22 +1941,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - en.ilsole24ore.com</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 07:00:00 GMT</t>
+          <t>Wed, 09 Sep 2026 14:15:55 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOeC1LTzN2WUwxbTVYM19qY0J3VlJZYkU3MVJ5NU0yaS1odGFuVnNIY0hLS1Z1SWhWMlJIdHpVZ1BwNVhpbkVCMUY4NjJVSTJybHhiVGtaWmk5Rkhvdm5zSk9nUVVLN0YyRzdVMUN5QUFRRS1POENGdFMzVFg5THJzcHlmZnZOQUtXdXdZdDNVb1d0Q1NFWWlOemZoWFdyYVBNT1VGR2tPSFJsQjJLaE9BeHhvMm1yWGZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZG5SeXlXUnVvYkw5OTFoZEgwUEVqem5wRE5vSmllckF5RlZxWVRZbzVJX2dycF9CeWtzTlBGejF3djNWelJpd0c3dVZieUktdjNQNVVTSWpKVkNFbURlcjdFOVE5bWhlekFIa3VNS1NQVktXUEU0TWc3cjhheDgyc1VNUjNLcllxZHZhcFlmbV9oakJwMGFfb1BZclBuTzZZN3lkRThITUNrdUhCOTlDV2hvQQ?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - en.ilsole24ore.com</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>en.ilsole24ore.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>
@@ -2121,40 +2121,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
+          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:50+00:00</t>
+          <t>2026-09-10T21:40:21+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
+          <t>I migliori 3 fondi azionari income - Morningstar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:00:00 GMT</t>
+          <t>Thu, 22 May 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5yMVBmdkdBZkZCV1dIU0x4dmpQVVp6U28tcW9aSG1ZeW9pak1CN09ZLXdTOENVNnV3SnBWUGg5Y0plTzhLS0hmeGVzeUhaTGpwQlh6emZiX0d3VUt1MXhLZmFJU1BNeEFZN09tMF9mVVdqOW5jRjN0WE5NZjFPZW8?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I migliori 3 fondi azionari income - Morningstar</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thu, 22 May 2025 07:00:00 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5yMVBmdkdBZkZCV1dIU0x4dmpQVVp6U28tcW9aSG1ZeW9pak1CN09ZLXdTOENVNnV3SnBWUGg5Y0plTzhLS0hmeGVzeUhaTGpwQlh6emZiX0d3VUt1MXhLZmFJU1BNeEFZN09tMF9mVVdqOW5jRjN0WE5NZjFPZW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -921,22 +921,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
+          <t>Gli ETF più popolari del trimestre - Morningstar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Sat, 28 Jun 2025 23:59:51 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbDFGNWY3WS1FT0tmdkZMc1k4QlVLUmhQOExzcE45T1VmWDBYWGZOeENJVGFhMS16ajcydFNaUFdwRkNxZ183X1AxNkh0NGR0RGdyYzN0Q196bndPVDRNWVBKQi1JZ1oyaDJHWTA2Qlc1ZmxaamI1Tm1sN2tRWnloTmN3?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -981,40 +981,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gold: Inflation data key catalyst – TD Securities - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:17:56 GMT</t>
+          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZW5USVloaXo1bEtJNlRqNXJqdnlRSE1FQzJrSmQ1dmd5bmQ5QTFkbGdIYnZjNTFRemtLdGc0dkYyUzdNOHVZSFBQaThjRE5lS2JuR2p4SFppczJVcGN4ODlyRzFXX0Z2T1NrZ2tBeHdqM2pMd1VlT0wtTEtLUEpmNVYyVnlzNktxWmZIbXUyV1ZoczlBNmd1aGV5NldDNVdHT3pmNmVlVi1EV00xa0kyTVh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1041,40 +1041,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,40 +1101,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Mon, 31 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,40 +1161,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gold: Inflation data key catalyst – TD Securities - tmgm.com</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:17:56 GMT</t>
+          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZW5USVloaXo1bEtJNlRqNXJqdnlRSE1FQzJrSmQ1dmd5bmQ5QTFkbGdIYnZjNTFRemtLdGc0dkYyUzdNOHVZSFBQaThjRE5lS2JuR2p4SFppczJVcGN4ODlyRzFXX0Z2T1NrZ2tBeHdqM2pMd1VlT0wtTEtLUEpmNVYyVnlzNktxWmZIbXUyV1ZoczlBNmd1aGV5NldDNVdHT3pmNmVlVi1EV00xa0kyTVh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,40 +1341,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
+          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,40 +1401,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BoE's Bailey defends central bank flexibility, warns of bond market pressures - tmgm.com</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fri, 04 Sep 2026 10:34:43 GMT</t>
+          <t>Mon, 31 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPX1oyV1lCVmZOZFFmM0tHaGVPNFlaYjlQd2hEVWYzZjRVRUJVb1VLUHhJeHZqcDFlRk44ajNLYksyMVJJSnp3Sk5jZUk1QldFcmpxVHdFMFJZZmVtZzBleEtWc2JRcUxXbFYyS0VyRDVfNF9wUnVSZGhub196blo4THRhZFpzLUVKaGFsRWV3ZmR3aGVvOEtJS3VKS2R3eHNtVmE1NlczdDdjb0Y3Z3M1SEphdFlseXk4ckF0aWJ4R054MDdaSmg1aFR2cDZMZnd4OWk3bmo3S0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,40 +1461,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 05:30:10 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1521,26 +1521,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,30 +1651,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,30 +1711,30 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mon, 29 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
+          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
+          <t>Mon, 29 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
+          <t>Stock markets: a lull ahead of US inflation figures. Avio soars in Milan - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1891,30 +1891,30 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 05:43:19 GMT</t>
+          <t>Fri, 11 Sep 2026 05:25:07 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSHRqc0s0UU8yZjJzXzJCU3luQzRPRE14RnlVOWZCY3JMcHVlb2NObktDamE1X2lsbDFzcmZZTnpzTWY4TmxIeWRYb05NU2tNY3hwVUt6RWFHMXYtX3pJeHJqOFNjRE1LNHRDbnptdWNsRXN6YTVDZ3JBeDQ5NUcwT3pELVNURlF1cDVVTmdvT0pKZE1tTm1QamVGbmZTUW82NEZKOXVZWHhyQ0hoOS1MN21Bdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxORFE2SVFNTDBZNVRBbkR1QVAySnBIWGVJMC1BZGFYQ19MOE5LR2ZzaXhwTkJzUWxoOGkzbW14VDdBXy1UcE0wX2JIVUJPVFI4anRrQ2Q5SmFCdVNSVWVxbFRPanp3ZDU4M0IzN1RKTGNqNUxyX2xNOHNSbTZaMl9QNHhJWDVKNzhrXzRrRA?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe pesare su azionario europeo</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
+          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1951,30 +1951,30 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 14:15:55 GMT</t>
+          <t>Wed, 09 Sep 2026 05:43:19 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZG5SeXlXUnVvYkw5OTFoZEgwUEVqem5wRE5vSmllckF5RlZxWVRZbzVJX2dycF9CeWtzTlBGejF3djNWelJpd0c3dVZieUktdjNQNVVTSWpKVkNFbURlcjdFOVE5bWhlekFIa3VNS1NQVktXUEU0TWc3cjhheDgyc1VNUjNLcllxZHZhcFlmbV9oakJwMGFfb1BZclBuTzZZN3lkRThITUNrdUhCOTlDV2hvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSHRqc0s0UU8yZjJzXzJCU3luQzRPRE14RnlVOWZCY3JMcHVlb2NObktDamE1X2lsbDFzcmZZTnpzTWY4TmxIeWRYb05NU2tNY3hwVUt6RWFHMXYtX3pJeHJqOFNjRE1LNHRDbnptdWNsRXN6YTVDZ3JBeDQ5NUcwT3pELVNURlF1cDVVTmdvT0pKZE1tTm1QamVGbmZTUW82NEZKOXVZWHhyQ0hoOS1MN21Bdw?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,40 +2001,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,40 +2061,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Wed, 09 Sep 2026 14:15:55 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZG5SeXlXUnVvYkw5OTFoZEgwUEVqem5wRE5vSmllckF5RlZxWVRZbzVJX2dycF9CeWtzTlBGejF3djNWelJpd0c3dVZieUktdjNQNVVTSWpKVkNFbURlcjdFOVE5bWhlekFIa3VNS1NQVktXUEU0TWc3cjhheDgyc1VNUjNLcllxZHZhcFlmbV9oakJwMGFfb1BZclBuTzZZN3lkRThITUNrdUhCOTlDV2hvQQ?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2121,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ECB: Lagarde says war is weighing on economic activity, but manufacturing is holding up - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVDBOeXo2azBUd2NiUUpBakRVYkEtZmhjUW1xT1FYaG1OSDJHdnVxRVJqRE5UY2dOTjNxTTdtSVQwWFJURGxaZV80R0RMb1JhYnpDSzFUS2xzcEtydU5DZlFheElNOFBJYnFmdFZHcURBeTNCb0oxNXJnYW5TRzFjZFhHQnZsVk1qWVV1SjdMLVlUTndLeUsyUEhJTGFqSG9ZU2VqOFFkbk04QmwxdnBPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:21+00:00</t>
+          <t>2026-09-11T12:14:05+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - Wall Street Italia</t>
+          <t>Interview with Peter Elston - wallstreetitalia.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wall Street Italia</t>
+          <t>wallstreetitalia.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -991,30 +991,30 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
+          <t>Mon, 31 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1111,30 +1111,30 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mon, 31 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,26 +1161,26 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,40 +1221,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
+          <t>Financial Stability Report, No. 1 - 2025 - bancaditalia.it</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>bancaditalia.it</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 29 Apr 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbC1EbWpWaFFRNUxpS0tVTFFwbDFSQjhmQVFwbUNNNnhqaFhJQlNqWG1nTGNySGZUcWhCbTM0cEhrT2dYU1NNeVNTelBYOGhqZVR2Q1hUc1MxN29uRVk0ckpvWkVpTGowVHNTb1Nmb0lqTnFfamw5WVVkQlI2ZXFwUmJEQ3Mtd1pBTC1oZVBtbnBYQ2lPLUkwekhWbGJCMXk2WVh1cWQ1SzkyNlFQbndFYktBeWw5QQ?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1291,30 +1291,30 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
+          <t>Mon, 31 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale supporto di breve periodo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stock market: global flight from bonds spills over into share prices, with Milan (-1.3 per cent) bringing up the rear - Il Sole 24 ORE</t>
+          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1411,30 +1411,30 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mon, 31 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNVWMwancxUTFFdktQWXJLOWw4dF9xOVRuQWZsdmNuTE56Q0M2bHotRXZLeEIteGFSUkg1U0gzdERLX2xPWGtoaFNzb1NFX0x6RlVIQ2dyeEV1VXUtMVNma0Z6MGFlQzFQNlBYMFVvSnV6TnpwWlBYSk9rYUVMVm5YemxQNFYwNE5JNmRjNzB1NUZxbDduWDRFMUxVYlN2TU5IVTY1clpPOW9Rd3JwTEJHWG9HakFrR3E2ekVsZ2tua1BISXFWZGhXYU52OE1FbkhlQ1MtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Potenziale supporto di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,26 +1461,26 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
+          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1521,40 +1521,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
+          <t>Financial Stability Report, No. 1 - 2025 - bancaditalia.it</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>bancaditalia.it</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 29 Apr 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbC1EbWpWaFFRNUxpS0tVTFFwbDFSQjhmQVFwbUNNNnhqaFhJQlNqWG1nTGNySGZUcWhCbTM0cEhrT2dYU1NNeVNTelBYOGhqZVR2Q1hUc1MxN29uRVk0ckpvWkVpTGowVHNTb1Nmb0lqTnFfamw5WVVkQlI2ZXFwUmJEQ3Mtd1pBTC1oZVBtbnBYQ2lPLUkwekhWbGJCMXk2WVh1cWQ1SzkyNlFQbndFYktBeWw5QQ?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:05+00:00</t>
+          <t>2026-09-11T14:29:30+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Interview with Peter Elston - wallstreetitalia.com</t>
+          <t>Interview with Peter Elston - Wall Street Italia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>wallstreetitalia.com</t>
+          <t>Wall Street Italia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I migliori 3 fondi azionari income - Morningstar</t>
+          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thu, 22 May 2025 07:00:00 GMT</t>
+          <t>Mon, 11 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5yMVBmdkdBZkZCV1dIU0x4dmpQVVp6U28tcW9aSG1ZeW9pak1CN09ZLXdTOENVNnV3SnBWUGg5Y0plTzhLS0hmeGVzeUhaTGpwQlh6emZiX0d3VUt1MXhLZmFJU1BNeEFZN09tMF9mVVdqOW5jRjN0WE5NZjFPZW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
+          <t>ETF JEGP | JPM Global Equity Premium Income Active UCITS ETF - USD (dist) quotazione - Investing.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
+          <t>Mon, 18 Dec 2023 08:07:52 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE8xd2tXUWdWMlVXSm43OGltTWRyaC10N1pTN21XSS1tbkhjZ1poODJQWVpYMzhfckY2Z1o3OUhZV09zYld1N0ZfYXdJVzE0V2tpVzEw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gli ETF più popolari del trimestre - Morningstar</t>
+          <t>I migliori 3 fondi azionari income - Morningstar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sat, 28 Jun 2025 23:59:51 GMT</t>
+          <t>Thu, 22 May 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbDFGNWY3WS1FT0tmdkZMc1k4QlVLUmhQOExzcE45T1VmWDBYWGZOeENJVGFhMS16ajcydFNaUFdwRkNxZ183X1AxNkh0NGR0RGdyYzN0Q196bndPVDRNWVBKQi1JZ1oyaDJHWTA2Qlc1ZmxaamI1Tm1sN2tRWnloTmN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5yMVBmdkdBZkZCV1dIU0x4dmpQVVp6U28tcW9aSG1ZeW9pak1CN09ZLXdTOENVNnV3SnBWUGg5Y0plTzhLS0hmeGVzeUhaTGpwQlh6emZiX0d3VUt1MXhLZmFJU1BNeEFZN09tMF9mVVdqOW5jRjN0WE5NZjFPZW8?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stock markets: pressure eases on bonds and oil. Lottomatica plummets in Milan (-0.2 per cent) - Il Sole 24 ORE</t>
+          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1651,30 +1651,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 07:00:00 GMT</t>
+          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUkl3U1N4Rk9hT25EUlBGRE84dHYwaUlVdnhzQVRhYjRScUpTVGFHcHFSQmRDTE1NUkM2Y1FKMm9oVE9qT3QxdlBWRnhxLVdsTm8wNkhVQkVYR3o3T3pESjROa2tyV2pPVm13NEJQOS1ndmhnSEsxNm1BSXZSOVE3dDB2YWp0ZmFSd19qYWcxVGUyOWowYndDOHQxZVNONkhmUmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tech sell-offs weigh on the stock markets; Milan down 1.5% as St plummets - Il Sole 24 ORE</t>
+          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1711,30 +1711,30 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPU2ZQS1VNX2JEZzVnaXZxSVNmcnN3NUhIRUV4OWU1ZGstOTQ3QXpFN1JXMVhPWGpocmd1MDI3LVdoVjZ1Skw3cDFBTTZ6dEx5TEdmWVJucGs4dWMxNkxOLWNEYnYyUTBfbkJNUWh3MmlpOVQwOS1vd2R4WFh1RXo2Z0R2aFphWEp0a3M2djM5eFQxNG1DMDUxOS14MVEwOGxsTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Potenziale pressione negativa di breve periodo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The war hasn’t stopped the Tel Aviv Stock Exchange: up 100 per cent from its lows and a new record for 2026 - Il Sole 24 ORE</t>
+          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+          <t>Mon, 29 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU1BRc3pON1dhZW1BVV9WVEpETWg3VzFtU2QwdF9sRkplYm5WZUdVQ2wzSkRackNjQkNaRjBSV19kSE1LT2dUVF95a2pOb3dYdXRHa3hyS2lCZWJwTS1MQy1jN0U4cTc0Mm1URDhBT2xMVVpDeGVUb2F3SkJpd1dZZEpkeTgtTU9QTzVSQjM5elAyeHBwaHE3aTNGemc3S05iRktLdmVIWDgwSUdxU3BpUVBRZV9SdVBJb0kxWGFYSmN2SGswQmRVdmd2bTN4amZjTGo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stock markets: Milan (+15%) finishes the half-year at the top of the class - Il Sole 24 ORE</t>
+          <t>Emerging markets, why Eastern European stock markets are record-breakers - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mon, 29 Jun 2026 07:00:00 GMT</t>
+          <t>Sat, 04 Oct 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1dlN0FBMDdONGxKTnRtZWlVVDVlNDdES3JkZVlGTXlubk0zWjdhaExvTXVSY3B6OGdvMHNlZUM2WTZSUFNTR0dTaGtSTDRXMDhTYzFjRFJZbmY4Zzc0emNyQjBvU0RwdkpTZF9uR3BsR2tHbDBBUXdrLUxEbnFRdkJqNU9JWkFxdFN2dGFQUU9rM0dLRFRENnZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNTFd5cGFuOGd2S2pCVktkRTBmVmh3eHpnYm9PZUpyeGdMdmhkTWI4cmRTZkxSbWpwWWVGckxWcDIwc0taQ3JtazVpRXNIYlQ5QnVYUnBGRGNtREZFSkw1SUhhbjFpcm1pc1R1bkc2a2lpTkZZMzFEUWFtZEFLYWJUazBCRVRnb1U0R1MwOE03MkFJc09pclBEUXc1cw?oc=5</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,22 +2001,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>tmgm.com</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
+          <t>Wed, 09 Sep 2026 14:15:55 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZG5SeXlXUnVvYkw5OTFoZEgwUEVqem5wRE5vSmllckF5RlZxWVRZbzVJX2dycF9CeWtzTlBGejF3djNWelJpd0c3dVZieUktdjNQNVVTSWpKVkNFbURlcjdFOVE5bWhlekFIa3VNS1NQVktXUEU0TWc3cjhheDgyc1VNUjNLcllxZHZhcFlmbV9oakJwMGFfb1BZclBuTzZZN3lkRThITUNrdUhCOTlDV2hvQQ?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,40 +2061,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - lastampa.it</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>lastampa.it</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 14:15:55 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZG5SeXlXUnVvYkw5OTFoZEgwUEVqem5wRE5vSmllckF5RlZxWVRZbzVJX2dycF9CeWtzTlBGejF3djNWelJpd0c3dVZieUktdjNQNVVTSWpKVkNFbURlcjdFOVE5bWhlekFIa3VNS1NQVktXUEU0TWc3cjhheDgyc1VNUjNLcllxZHZhcFlmbV9oakJwMGFfb1BZclBuTzZZN3lkRThITUNrdUhCOTlDV2hvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2121,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>La Stampa</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:30+00:00</t>
+          <t>2026-09-11T17:02:07+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I migliori fondi azionari globali orientati al reddito - Morningstar</t>
+          <t>I migliori fondi azionari globali orientati al reddito - global.morningstar.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>global.morningstar.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net</t>
+          <t>Capital One Announces Quarterly Dividend - 01net.it</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>01net.it</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -801,22 +801,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3 titoli azionari USA ad alto dividendo per maggio 2026 - Morningstar</t>
+          <t>I migliori 3 fondi azionari income - global.morningstar.com</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>global.morningstar.com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 07:00:00 GMT</t>
+          <t>Thu, 22 May 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZ3hzcHJrSkd1dGd5eTZHSm5kamwyRXJRM1pQdy10YXJzaWdXZEFibHZoam1GTFNOUm1fNGdtaTNlRTN2REFGdlhTeGFNTlpKTUNqMUFYei1xNHV5S09RNEEtcVVOd0UzMFZLRmkzUHRTaE9ZMGhCbzg4cFZUUWJIUzdBQTNKaHpzV3NiMVJXdnNYX3pONGozM1pGUnU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5yMVBmdkdBZkZCV1dIU0x4dmpQVVp6U28tcW9aSG1ZeW9pak1CN09ZLXdTOENVNnV3SnBWUGg5Y0plTzhLS0hmeGVzeUhaTGpwQlh6emZiX0d3VUt1MXhLZmFJU1BNeEFZN09tMF9mVVdqOW5jRjN0WE5NZjFPZW8?oc=5</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ETF JEGP | JPM Global Equity Premium Income Active UCITS ETF - USD (dist) quotazione - Investing.com</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - it.tradingview.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>it.tradingview.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mon, 18 Dec 2023 08:07:52 GMT</t>
+          <t>Tue, 01 Aug 2017 20:10:55 GMT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE8xd2tXUWdWMlVXSm43OGltTWRyaC10N1pTN21XSS1tbkhjZ1poODJQWVpYMzhfckY2Z1o3OUhZV09zYld1N0ZfYXdJVzE0V2tpVzEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8tVHBZNUtoeGhPY3BUd2I5TzdscGRScHVlblhhV0JvSktiM2MwdHpqMXNDYlY2YzVNUFBxLTgzRXZfZmtSSjl3MVdCN2czUnlaN0liUjNpZw?oc=5</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -921,22 +921,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I migliori 3 fondi azionari income - Morningstar</t>
+          <t>Gli ETF più popolari del trimestre - global.morningstar.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>global.morningstar.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thu, 22 May 2025 07:00:00 GMT</t>
+          <t>Sat, 28 Jun 2025 23:59:51 GMT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5yMVBmdkdBZkZCV1dIU0x4dmpQVVp6U28tcW9aSG1ZeW9pak1CN09ZLXdTOENVNnV3SnBWUGg5Y0plTzhLS0hmeGVzeUhaTGpwQlh6emZiX0d3VUt1MXhLZmFJU1BNeEFZN09tMF9mVVdqOW5jRjN0WE5NZjFPZW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbDFGNWY3WS1FT0tmdkZMc1k4QlVLUmhQOExzcE45T1VmWDBYWGZOeENJVGFhMS16ajcydFNaUFdwRkNxZ183X1AxNkh0NGR0RGdyYzN0Q196bndPVDRNWVBKQi1JZ1oyaDJHWTA2Qlc1ZmxaamI1Tm1sN2tRWnloTmN3?oc=5</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stock markets: a lull ahead of US inflation figures. Avio soars in Milan - Il Sole 24 ORE</t>
+          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1891,30 +1891,30 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 05:25:07 GMT</t>
+          <t>Wed, 09 Sep 2026 05:43:19 GMT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxORFE2SVFNTDBZNVRBbkR1QVAySnBIWGVJMC1BZGFYQ19MOE5LR2ZzaXhwTkJzUWxoOGkzbW14VDdBXy1UcE0wX2JIVUJPVFI4anRrQ2Q5SmFCdVNSVWVxbFRPanp3ZDU4M0IzN1RKTGNqNUxyX2xNOHNSbTZaMl9QNHhJWDVKNzhrXzRrRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSHRqc0s0UU8yZjJzXzJCU3luQzRPRE14RnlVOWZCY3JMcHVlb2NObktDamE1X2lsbDFzcmZZTnpzTWY4TmxIeWRYb05NU2tNY3hwVUt6RWFHMXYtX3pJeHJqOFNjRE1LNHRDbnptdWNsRXN6YTVDZ3JBeDQ5NUcwT3pELVNURlF1cDVVTmdvT0pKZE1tTm1QamVGbmZTUW82NEZKOXVZWHhyQ0hoOS1MN21Bdw?oc=5</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Attenzione / pressione negativa</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Potrebbe pesare su azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sky-high crude oil prices send stock markets into the red. Milan limits the damage (-0.6 per cent) thanks to Eni - Il Sole 24 ORE</t>
+          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1951,30 +1951,30 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 05:43:19 GMT</t>
+          <t>Wed, 09 Sep 2026 14:15:55 GMT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSHRqc0s0UU8yZjJzXzJCU3luQzRPRE14RnlVOWZCY3JMcHVlb2NObktDamE1X2lsbDFzcmZZTnpzTWY4TmxIeWRYb05NU2tNY3hwVUt6RWFHMXYtX3pJeHJqOFNjRE1LNHRDbnptdWNsRXN6YTVDZ3JBeDQ5NUcwT3pELVNURlF1cDVVTmdvT0pKZE1tTm1QamVGbmZTUW82NEZKOXVZWHhyQ0hoOS1MN21Bdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZG5SeXlXUnVvYkw5OTFoZEgwUEVqem5wRE5vSmllckF5RlZxWVRZbzVJX2dycF9CeWtzTlBGejF3djNWelJpd0c3dVZieUktdjNQNVVTSWpKVkNFbURlcjdFOVE5bWhlekFIa3VNS1NQVktXUEU0TWc3cjhheDgyc1VNUjNLcllxZHZhcFlmbV9oakJwMGFfb1BZclBuTzZZN3lkRThITUNrdUhCOTlDV2hvQQ?oc=5</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,40 +2001,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oil at $100 a barrel and bond yields send stock markets into the red; Eni surges in Milan - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - lastampa.it</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>lastampa.it</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 14:15:55 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZG5SeXlXUnVvYkw5OTFoZEgwUEVqem5wRE5vSmllckF5RlZxWVRZbzVJX2dycF9CeWtzTlBGejF3djNWelJpd0c3dVZieUktdjNQNVVTSWpKVkNFbURlcjdFOVE5bWhlekFIa3VNS1NQVktXUEU0TWc3cjhheDgyc1VNUjNLcllxZHZhcFlmbV9oakJwMGFfb1BZclBuTzZZN3lkRThITUNrdUhCOTlDV2hvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Potenzialmente favorevole</t>
+          <t>Neutro / da monitorare</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Potrebbe supportare azionario europeo</t>
+          <t>Da monitorare: impatto non evidente</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - lastampa.it</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>lastampa.it</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Stock markets: the fall in crude oil prices is not enough. Defence and luxury sectors weigh on Milan (-0.1%) - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Sun, 21 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQT1pnbjdlTkRwLXhzLWdOQm5XVFM5WVYyRG1CUTdxSkRJd3kwb3JmUzBUYlRPRFBRTFJtd2IyUjJmWktXaURRTFlhMW9KLXV3X2FnYS1zZnJodnZSM1FobkhtZXB6OHdQdjFvY2FDZXFObzIwOWNwWjFIUkdqbkxYWjZCeks1YjZSUXBQUFctcUpwcUdPN3o4TmxhYw?oc=5</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:07+00:00</t>
+          <t>2026-09-11T19:10:01+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_News_Radar.xlsx
+++ b/AlphaForge_News_Radar.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I migliori fondi azionari globali orientati al reddito - global.morningstar.com</t>
+          <t>I migliori fondi azionari globali orientati al reddito - Morningstar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>global.morningstar.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Capital One Announces Quarterly Dividend - 01net.it</t>
+          <t>Capital One Announces Quarterly Dividend - 01net</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01net.it</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I migliori 3 fondi azionari income - global.morningstar.com</t>
+          <t>I migliori 3 fondi azionari income - Morningstar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>global.morningstar.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - it.tradingview.com</t>
+          <t>Prezzo e grafico del fondo RFI — NYSE:RFI - TradingView</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>it.tradingview.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gli ETF più popolari del trimestre - global.morningstar.com</t>
+          <t>Gli ETF più popolari del trimestre - Morningstar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>global.morningstar.com</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1161,26 +1161,26 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1221,40 +1221,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Financial Stability Report, No. 1 - 2025 - bancaditalia.it</t>
+          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>bancaditalia.it</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tue, 29 Apr 2025 07:00:00 GMT</t>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbC1EbWpWaFFRNUxpS0tVTFFwbDFSQjhmQVFwbUNNNnhqaFhJQlNqWG1nTGNySGZUcWhCbTM0cEhrT2dYU1NNeVNTelBYOGhqZVR2Q1hUc1MxN29uRVk0ckpvWkVpTGowVHNTb1Nmb0lqTnFfamw5WVVkQlI2ZXFwUmJEQ3Mtd1pBTC1oZVBtbnBYQ2lPLUkwekhWbGJCMXk2WVh1cWQ1SzkyNlFQbndFYktBeWw5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,26 +1461,26 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
+          <t>Gold Price Forecast: XAU/USD holds onto early losses near $4,630, US Yields plunge - tmgm.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
+          <t>Tue, 25 Aug 2026 10:40:12 GMT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNOXBIS0s4SG12cFQweGNELVJYMmRXS25SUmY0OWlxRWs0THFrdElORVZfODNZN2p4RFpyX3FEZnA4eHhMNkx5eHllRC1yU3NmLWdBaC1WVEppUnhSTXBPeFhZNVFVZDBSdjI2UDU4Vk1SNGczcWRrRkx1Rk94YlVtTWk2Tm94SDRET3dVUEpXRDZVcjZKdk1tNXdaZHpYOXU1RFU5WjFRWnNiLWJaMmxUUnN6NmMxdmhnUzJtNGg2NmNxanpJZ2pjRjB4REZuajZ1Q29zVTVzNVJqdndPaEE?oc=5</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1521,40 +1521,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Financial Stability Report, No. 1 - 2025 - bancaditalia.it</t>
+          <t>Stock markets: a period of stability is expected until early 2027. All eyes are on inflation - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>bancaditalia.it</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tue, 29 Apr 2025 07:00:00 GMT</t>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbC1EbWpWaFFRNUxpS0tVTFFwbDFSQjhmQVFwbUNNNnhqaFhJQlNqWG1nTGNySGZUcWhCbTM0cEhrT2dYU1NNeVNTelBYOGhqZVR2Q1hUc1MxN29uRVk0ckpvWkVpTGowVHNTb1Nmb0lqTnFfamw5WVVkQlI2ZXFwUmJEQ3Mtd1pBTC1oZVBtbnBYQ2lPLUkwekhWbGJCMXk2WVh1cWQ1SzkyNlFQbndFYktBeWw5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNalplNkgxQXJWM3JhTWxPWmczMFJoaXZHTHc3US1xY0VOR0V6RUVXZ0JBcjUwVzNSUVJabDIxb1A2SjJQTlJmUXNadGpGZ252elU5UjFLazZ5cS1vZFRhRXc2UFZaWUZLZFFwZXJUZW45b29XNkdremt6ZlR6OS1WYnYzWHlFNC16b24zRHFxQm1DN3BQT2NtTDktQW1tcENUWmU4bndOV3RLdUtXVUNiU3plQ3U0bjJoVzdxcUhNNl80VzZR?oc=5</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Attenzione / pressione negativa</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potenziale pressione negativa di breve periodo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,40 +2001,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - lastampa.it</t>
+          <t>Euro recovers some early losses against Japanese Yen, ECB policy in focus - tmgm.com</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>lastampa.it</t>
+          <t>tmgm.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
+          <t>Tue, 08 Sep 2026 08:55:19 GMT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNU0x0bld1ZkJpWHRQTjhOa0JKQ0xhMDB4bHdqYldaYzVHMmVsdlkzaWJEaXlNck1nSEhlM0tvTjJTWnJFWDktX0dnYzR4Q2tYaV9yNGNIWkFMbXZReHIweE1kdUlkX3B3Y0d3X0dqcXc3akt3TFJiWGZhd25LaGVSenVoNEZkVW5zaEp1TnFlbmctdXEyZjVkRUNhckx2aXBsd0k4T01tUE9RQVdFTXNkMW1ObkZYZWhUeGJQRkRZcC05TFpwRUlRVVBiZm1zWEp5Tk9Ydg?oc=5</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Neutro / da monitorare</t>
+          <t>Potenzialmente favorevole</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Da monitorare: impatto non evidente</t>
+          <t>Potrebbe supportare azionario europeo</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
+          <t>Villeroy: “Economy and markets increasingly Uncertain. ECB will raise interest rates if necessary” - La Stampa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>La Stampa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+          <t>Sun, 29 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOR0lWREN6ajRDSWZKTVAwX3gxamFSbk1yUFdNOG1yQkRBcWpsVzZadk4yUWp0ZFpBUFUyOWZHaGR1XzdkdFo3ZzNsRkR5bW9maWd5WThZNC1xaElvRVNReDdWOGVnTVAwMDUyclgzc1dGNngtYlJuU2ptUlRWcVcxekwxUFpNbzVlSVRpbHdJOWs5aXpBTTBSRElmQzlqTjB6Njg0cUtuSnU3Qm9TMEIzVDVybi1JamtTX2ZzTF9rQ0MxX3o3X2Y3cVhJS2MxMjJEaHF4QlhseEVpREl3a3B0TjdmNzU3NXJC0gHuAUFVX3lxTE9kQmloSlFESHNzenJTTkJ3TVllN3JoZ0RsRnhOSF8tN014T1FaN0xIYXBfd1dibDBxWl9vZ01oVWhaSEdrX05DYW9Tb1VkV2o1MGtPc2Rwd29QRGxaMUc5N0lmRGs1M3E1UVhGY2tpLXhndnB2aVZUMzQxUWpfaVJrbWZ0VHFuWTlhc1hwdGo4SU5YS2k0TjZCTFJIVUFDWmZYUUp2dzFGQTQ5d3JQWldOaUFlZDdPbWZXVU4xejJHeFdLY1BxZU9JbHd2Z3BBWVdwZ3ZndzJzLTVkUTJJaDhtMVdvY2hId29GOTU2Wnc?oc=5</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stock markets: the fall in crude oil prices is not enough. Defence and luxury sectors weigh on Milan (-0.1%) - Il Sole 24 ORE</t>
+          <t>The SpaceX effect is boosting the stock markets. Wall Street closes on a high note following Trump’s announcements on Iran - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 07:00:00 GMT</t>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQT1pnbjdlTkRwLXhzLWdOQm5XVFM5WVYyRG1CUTdxSkRJd3kwb3JmUzBUYlRPRFBRTFJtd2IyUjJmWktXaURRTFlhMW9KLXV3X2FnYS1zZnJodnZSM1FobkhtZXB6OHdQdjFvY2FDZXFObzIwOWNwWjFIUkdqbkxYWjZCeks1YjZSUXBQUFctcUpwcUdPN3o4TmxhYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcEFtdkJaenVSNVVnTGt3aWN5czU1T2ZReGFaVmtWdTQxZ21iS0VXTUNiVGlkd3ZZWXlja2hyVUVwQkJtUktNMHhnSFVoR1gxWUJoMVd6NVhlLThpRFk2c1Z3b0pEOHVQdlA1MEhNUmdpa25NVm5UNV9mc05lblV3Slh1NGFyXy1BNGVSN3R6ZkZoVzJ4QVMxaWxhemhIVm1KMUE?oc=5</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-11T19:10:01+00:00</t>
+          <t>2026-09-11T21:45:20+00:00</t>
         </is>
       </c>
     </row>
